--- a/Pricing-October-Data.xlsx
+++ b/Pricing-October-Data.xlsx
@@ -169,8 +169,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Results" displayName="Results" ref="A1:I34" headerRowCount="1">
-  <autoFilter ref="A1:I34"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Results" displayName="Results" ref="A1:I47" headerRowCount="1">
+  <autoFilter ref="A1:I47"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Series"/>
     <tableColumn id="2" name="Game"/>
@@ -187,8 +187,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="LatestPrices" displayName="LatestPrices" ref="A1:J69" headerRowCount="1">
-  <autoFilter ref="A1:J69"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="LatestPrices" displayName="LatestPrices" ref="A1:J75" headerRowCount="1">
+  <autoFilter ref="A1:J75"/>
   <tableColumns count="10">
     <tableColumn id="1" name="Game"/>
     <tableColumn id="2" name="First pitch (UTC)"/>
@@ -206,8 +206,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Captures" displayName="Captures" ref="A1:K672" headerRowCount="1">
-  <autoFilter ref="A1:K672"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Captures" displayName="Captures" ref="A1:K738" headerRowCount="1">
+  <autoFilter ref="A1:K738"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Game"/>
     <tableColumn id="2" name="First pitch (UTC)"/>
@@ -226,8 +226,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Games" displayName="Games" ref="A1:I27" headerRowCount="1">
-  <autoFilter ref="A1:I27"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Games" displayName="Games" ref="A1:I8" headerRowCount="1">
+  <autoFilter ref="A1:I8"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Game"/>
     <tableColumn id="2" name="First pitch (UTC)"/>
@@ -244,8 +244,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="TicketmasterStatus" displayName="TicketmasterStatus" ref="A1:H26" headerRowCount="1">
-  <autoFilter ref="A1:H26"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="TicketmasterStatus" displayName="TicketmasterStatus" ref="A1:H8" headerRowCount="1">
+  <autoFilter ref="A1:H8"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Event"/>
     <tableColumn id="2" name="Date"/>
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2194,6 +2194,575 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>ALCS</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>Guardians 7-3; rally from 0-2 after 5th; road team wins</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>NLCS</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>Brewers 7-4; Contreras; lead 2-0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>ALCS</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>Rays 3-1; 3-run 4th on small ball; series tied 1-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>NLCS</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>Brewers 6-2; lead 3-0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>ALCS</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>Guardians 3-2; Williams wins; lead 2-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>NLCS</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>0-3</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>Brewers 6-4; sweep 4-0; first World Series since 1982; defending champs out</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>NLCS</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>0-4</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="n"/>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>not needed; cancelled after sweep</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>ALCS</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>Rays 7-3; series tied 2-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>ALCS</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>Rays 3-1; Rasmussen 7 IP; Rays lead 3-2; Guardians face elimination in Tampa</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>NLCS</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>4-0</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="n"/>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>not needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>ALCS</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>Rays 7-3; win ALCS 4-2; Caminero and Diaz 2-run HRs</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>NLCS</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>4-0</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="n"/>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>not needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>ALCS</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>4-2</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="n"/>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>not needed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -2208,7 +2777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J69"/>
+  <dimension ref="A1:J75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -4036,26 +4605,26 @@
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>2026-10-12T21:00</t>
+          <t>2026-10-12T23:00</t>
         </is>
       </c>
       <c r="D48" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>417</v>
+        <v>281</v>
       </c>
       <c r="F48" s="7" t="n">
-        <v>1334</v>
+        <v>859</v>
       </c>
       <c r="G48" s="8" t="n">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="H48" s="8" t="n">
-        <v>175</v>
+        <v>136</v>
       </c>
       <c r="I48" s="8" t="n">
-        <v>207.78</v>
+        <v>177.96</v>
       </c>
       <c r="J48" s="8" t="n">
         <v>1764</v>
@@ -4302,29 +4871,29 @@
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>2026-10-12T00:00</t>
+          <t>2026-10-13T23:00</t>
         </is>
       </c>
       <c r="D55" s="6" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>744</v>
+        <v>319</v>
       </c>
       <c r="F55" s="7" t="n">
-        <v>3173</v>
+        <v>1295</v>
       </c>
       <c r="G55" s="8" t="n">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="H55" s="8" t="n">
-        <v>258</v>
+        <v>141</v>
       </c>
       <c r="I55" s="8" t="n">
-        <v>303.84</v>
+        <v>200.34</v>
       </c>
       <c r="J55" s="8" t="n">
-        <v>11654</v>
+        <v>5680</v>
       </c>
     </row>
     <row r="56">
@@ -4454,29 +5023,29 @@
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>2026-10-12T00:00</t>
+          <t>2026-10-14T23:00</t>
         </is>
       </c>
       <c r="D59" s="6" t="n">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>1912</v>
+        <v>603</v>
       </c>
       <c r="F59" s="7" t="n">
-        <v>8019</v>
+        <v>2223</v>
       </c>
       <c r="G59" s="8" t="n">
-        <v>154</v>
+        <v>95</v>
       </c>
       <c r="H59" s="8" t="n">
-        <v>248</v>
+        <v>112</v>
       </c>
       <c r="I59" s="8" t="n">
-        <v>425.71</v>
+        <v>210.7</v>
       </c>
       <c r="J59" s="8" t="n">
-        <v>16431</v>
+        <v>4999</v>
       </c>
     </row>
     <row r="60">
@@ -4568,35 +5137,35 @@
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>2026-10-12T22:00</t>
+          <t>2026-10-15T16:00</t>
         </is>
       </c>
       <c r="D62" s="6" t="n">
-        <v>72</v>
+        <v>6</v>
       </c>
       <c r="E62" s="7" t="n">
-        <v>690</v>
+        <v>263</v>
       </c>
       <c r="F62" s="7" t="n">
-        <v>2648</v>
+        <v>1065</v>
       </c>
       <c r="G62" s="8" t="n">
-        <v>221</v>
+        <v>106</v>
       </c>
       <c r="H62" s="8" t="n">
-        <v>403</v>
+        <v>155</v>
       </c>
       <c r="I62" s="8" t="n">
-        <v>450.19</v>
+        <v>210.48</v>
       </c>
       <c r="J62" s="8" t="n">
-        <v>2218</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>TBD at Los Angeles Dodgers - NLCS (Home Game 2)</t>
+          <t>Milwaukee Brewers at Los Angeles Dodgers - NLCS (Game 4, Home Game 2)</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
@@ -4606,35 +5175,35 @@
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>2026-10-01T05:00</t>
+          <t>2026-10-15T23:00</t>
         </is>
       </c>
       <c r="D63" s="6" t="n">
-        <v>356</v>
+        <v>2</v>
       </c>
       <c r="E63" s="7" t="n">
-        <v>1987</v>
+        <v>541</v>
       </c>
       <c r="F63" s="7" t="n">
-        <v>9878</v>
+        <v>1908</v>
       </c>
       <c r="G63" s="8" t="n">
-        <v>174</v>
+        <v>70</v>
       </c>
       <c r="H63" s="8" t="n">
-        <v>276</v>
+        <v>101</v>
       </c>
       <c r="I63" s="8" t="n">
-        <v>503.42</v>
+        <v>226.68</v>
       </c>
       <c r="J63" s="8" t="n">
-        <v>20521</v>
+        <v>4545</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>TBD at Cleveland Guardians - ALCS (Home Game 2)</t>
+          <t>TBD at Chicago White Sox - ALCS (Game 4, Home Game 2)</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
@@ -4644,73 +5213,73 @@
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>2026-09-29T14:37</t>
+          <t>2026-10-01T03:00</t>
         </is>
       </c>
       <c r="D64" s="6" t="n">
-        <v>415.4</v>
+        <v>379</v>
       </c>
       <c r="E64" s="7" t="n">
-        <v>534</v>
+        <v>265</v>
       </c>
       <c r="F64" s="7" t="n">
-        <v>2619</v>
+        <v>1230</v>
       </c>
       <c r="G64" s="8" t="n">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="H64" s="8" t="n">
-        <v>473</v>
+        <v>531</v>
       </c>
       <c r="I64" s="8" t="n">
-        <v>493.45</v>
+        <v>903.11</v>
       </c>
       <c r="J64" s="8" t="n">
-        <v>1657</v>
+        <v>13040</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>TBD at Chicago White Sox - ALCS (Game 4, Home Game 2)</t>
+          <t>TBD at New York Yankees - ALCS (Home Game 3)</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>2026-10-16T22:00</t>
+          <t>2026-10-17T07:30</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>2026-10-01T03:00</t>
+          <t>2026-10-01T06:00</t>
         </is>
       </c>
       <c r="D65" s="6" t="n">
-        <v>379</v>
+        <v>385.5</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>265</v>
+        <v>576</v>
       </c>
       <c r="F65" s="7" t="n">
-        <v>1230</v>
+        <v>2522</v>
       </c>
       <c r="G65" s="8" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H65" s="8" t="n">
-        <v>531</v>
+        <v>623</v>
       </c>
       <c r="I65" s="8" t="n">
-        <v>903.11</v>
+        <v>1182.05</v>
       </c>
       <c r="J65" s="8" t="n">
-        <v>13040</v>
+        <v>11988</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>TBD at New York Yankees - ALCS (Home Game 3)</t>
+          <t>TBD at Atlanta Braves - NLCS (Home Game 3)</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
@@ -4727,136 +5296,364 @@
         <v>385.5</v>
       </c>
       <c r="E66" s="7" t="n">
-        <v>576</v>
+        <v>838</v>
       </c>
       <c r="F66" s="7" t="n">
-        <v>2522</v>
+        <v>4757</v>
       </c>
       <c r="G66" s="8" t="n">
-        <v>246</v>
+        <v>201</v>
       </c>
       <c r="H66" s="8" t="n">
-        <v>623</v>
+        <v>446</v>
       </c>
       <c r="I66" s="8" t="n">
-        <v>1182.05</v>
+        <v>802.95</v>
       </c>
       <c r="J66" s="8" t="n">
-        <v>11988</v>
+        <v>17780</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>TBD at Atlanta Braves - NLCS (Home Game 3)</t>
+          <t>TBD at Chicago White Sox - ALCS (Game 5, Home Game 3)</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>2026-10-17T07:30</t>
+          <t>2026-10-18T00:00</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>2026-10-01T06:00</t>
+          <t>2026-10-01T07:00</t>
         </is>
       </c>
       <c r="D67" s="6" t="n">
-        <v>385.5</v>
+        <v>401</v>
       </c>
       <c r="E67" s="7" t="n">
-        <v>838</v>
+        <v>175</v>
       </c>
       <c r="F67" s="7" t="n">
-        <v>4757</v>
+        <v>829</v>
       </c>
       <c r="G67" s="8" t="n">
-        <v>201</v>
+        <v>245</v>
       </c>
       <c r="H67" s="8" t="n">
-        <v>446</v>
+        <v>530</v>
       </c>
       <c r="I67" s="8" t="n">
-        <v>802.95</v>
+        <v>939.5700000000001</v>
       </c>
       <c r="J67" s="8" t="n">
-        <v>17780</v>
+        <v>14225</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>TBD at Cleveland Guardians - ALCS (Home Game 3)</t>
+          <t>Tampa Bay Rays at Cleveland Guardians - ALCS (Game 4, Home Game 2) (Formerly Game 5)</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
+          <t>2026-10-18T00:08</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
           <t>2026-10-18T00:00</t>
         </is>
       </c>
-      <c r="C68" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-01T06:00</t>
-        </is>
-      </c>
       <c r="D68" s="6" t="n">
-        <v>402</v>
+        <v>0.1</v>
       </c>
       <c r="E68" s="7" t="n">
-        <v>530</v>
+        <v>162</v>
       </c>
       <c r="F68" s="7" t="n">
-        <v>2609</v>
+        <v>379</v>
       </c>
       <c r="G68" s="8" t="n">
-        <v>257</v>
+        <v>90</v>
       </c>
       <c r="H68" s="8" t="n">
-        <v>506</v>
+        <v>202</v>
       </c>
       <c r="I68" s="8" t="n">
-        <v>530.84</v>
+        <v>239.11</v>
       </c>
       <c r="J68" s="8" t="n">
-        <v>1839</v>
+        <v>970</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>TBD at Chicago White Sox - ALCS (Game 5, Home Game 3)</t>
+          <t>Milwaukee Brewers at Los Angeles Dodgers - NLCS (Game 5, Home Game 3)</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>2026-10-18T00:00</t>
+          <t>2026-10-18T10:30</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>2026-10-01T07:00</t>
+          <t>2026-10-16T01:00</t>
         </is>
       </c>
       <c r="D69" s="6" t="n">
-        <v>401</v>
+        <v>57.5</v>
       </c>
       <c r="E69" s="7" t="n">
+        <v>1747</v>
+      </c>
+      <c r="F69" s="7" t="n">
+        <v>7290</v>
+      </c>
+      <c r="G69" s="8" t="n">
+        <v>91</v>
+      </c>
+      <c r="H69" s="8" t="n">
+        <v>220</v>
+      </c>
+      <c r="I69" s="8" t="n">
+        <v>419.93</v>
+      </c>
+      <c r="J69" s="8" t="n">
+        <v>25693</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays at Cleveland Guardians - ALCS (Game 5, Home Game 3) (Rescheduled Game 4 from 10/16)</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-18T21:08</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-18T21:00</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E70" s="7" t="n">
+        <v>33</v>
+      </c>
+      <c r="F70" s="7" t="n">
+        <v>48</v>
+      </c>
+      <c r="G70" s="8" t="n">
+        <v>167</v>
+      </c>
+      <c r="H70" s="8" t="n">
+        <v>374</v>
+      </c>
+      <c r="I70" s="8" t="n">
+        <v>459.27</v>
+      </c>
+      <c r="J70" s="8" t="n">
+        <v>1752</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>Los Angeles Dodgers at Milwaukee Brewers - NLCS (Game 6, Home Game 3)</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-19T00:00</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-16T00:00</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="E71" s="7" t="n">
+        <v>596</v>
+      </c>
+      <c r="F71" s="7" t="n">
+        <v>2562</v>
+      </c>
+      <c r="G71" s="8" t="n">
+        <v>302</v>
+      </c>
+      <c r="H71" s="8" t="n">
+        <v>586</v>
+      </c>
+      <c r="I71" s="8" t="n">
+        <v>695.47</v>
+      </c>
+      <c r="J71" s="8" t="n">
+        <v>4758</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians at Tampa Bay Rays - ALCS (Game 6, Home Game 3)</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-20T00:08</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-20T00:00</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E72" s="7" t="n">
+        <v>134</v>
+      </c>
+      <c r="F72" s="7" t="n">
+        <v>399</v>
+      </c>
+      <c r="G72" s="8" t="n">
+        <v>91</v>
+      </c>
+      <c r="H72" s="8" t="n">
         <v>175</v>
       </c>
-      <c r="F69" s="7" t="n">
-        <v>829</v>
-      </c>
-      <c r="G69" s="8" t="n">
-        <v>245</v>
-      </c>
-      <c r="H69" s="8" t="n">
-        <v>530</v>
-      </c>
-      <c r="I69" s="8" t="n">
-        <v>939.5700000000001</v>
-      </c>
-      <c r="J69" s="8" t="n">
-        <v>14225</v>
+      <c r="I72" s="8" t="n">
+        <v>207.63</v>
+      </c>
+      <c r="J72" s="8" t="n">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians at Tampa Bay Rays - ALCS (Game 7, Home Game 4)</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-21T00:08</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-20T01:00</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="E73" s="7" t="n">
+        <v>932</v>
+      </c>
+      <c r="F73" s="7" t="n">
+        <v>5428</v>
+      </c>
+      <c r="G73" s="8" t="n">
+        <v>111</v>
+      </c>
+      <c r="H73" s="8" t="n">
+        <v>269.5</v>
+      </c>
+      <c r="I73" s="8" t="n">
+        <v>355.26</v>
+      </c>
+      <c r="J73" s="8" t="n">
+        <v>6567</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays at Milwaukee Brewers - World Series (Game 1, Home Game 1)</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:00</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22T00:00</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="E74" s="7" t="n">
+        <v>274</v>
+      </c>
+      <c r="F74" s="7" t="n">
+        <v>767</v>
+      </c>
+      <c r="G74" s="8" t="n">
+        <v>2331</v>
+      </c>
+      <c r="H74" s="8" t="n">
+        <v>3977</v>
+      </c>
+      <c r="I74" s="8" t="n">
+        <v>4544.93</v>
+      </c>
+      <c r="J74" s="8" t="n">
+        <v>17655</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays at Milwaukee Brewers - World Series (Game 2, Home Game 2)</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-25T00:00</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22T00:00</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="E75" s="7" t="n">
+        <v>416</v>
+      </c>
+      <c r="F75" s="7" t="n">
+        <v>1149</v>
+      </c>
+      <c r="G75" s="8" t="n">
+        <v>2105</v>
+      </c>
+      <c r="H75" s="8" t="n">
+        <v>3943.5</v>
+      </c>
+      <c r="I75" s="8" t="n">
+        <v>4279.16</v>
+      </c>
+      <c r="J75" s="8" t="n">
+        <v>19420</v>
       </c>
     </row>
   </sheetData>
@@ -4873,7 +5670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K672"/>
+  <dimension ref="A1:K738"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -32598,7 +33395,7 @@
     <row r="645">
       <c r="A645" s="5" t="inlineStr">
         <is>
-          <t>TBD at Tampa Bay Rays - ALCS (Game 1, Home Game 1)</t>
+          <t>Cleveland Guardians at Tampa Bay Rays - ALCS (Game 1, Home Game 1)</t>
         </is>
       </c>
       <c r="B645" s="5" t="inlineStr">
@@ -32608,29 +33405,29 @@
       </c>
       <c r="C645" s="5" t="inlineStr">
         <is>
-          <t>2026-09-29T01:45</t>
+          <t>2026-10-12T23:00</t>
         </is>
       </c>
       <c r="D645" s="6" t="n">
-        <v>334.2</v>
+        <v>1</v>
       </c>
       <c r="E645" s="7" t="n">
-        <v>418</v>
+        <v>281</v>
       </c>
       <c r="F645" s="7" t="n">
-        <v>2559</v>
+        <v>859</v>
       </c>
       <c r="G645" s="8" t="n">
-        <v>199</v>
+        <v>61</v>
       </c>
       <c r="H645" s="8" t="n">
-        <v>369.5</v>
+        <v>136</v>
       </c>
       <c r="I645" s="8" t="n">
-        <v>447.78</v>
+        <v>177.96</v>
       </c>
       <c r="J645" s="8" t="n">
-        <v>8892</v>
+        <v>1764</v>
       </c>
       <c r="K645" s="5" t="inlineStr">
         <is>
@@ -32651,29 +33448,29 @@
       </c>
       <c r="C646" s="5" t="inlineStr">
         <is>
-          <t>2026-10-10T00:00</t>
+          <t>2026-09-29T01:45</t>
         </is>
       </c>
       <c r="D646" s="6" t="n">
-        <v>72</v>
+        <v>334.2</v>
       </c>
       <c r="E646" s="7" t="n">
-        <v>874</v>
+        <v>418</v>
       </c>
       <c r="F646" s="7" t="n">
-        <v>3991</v>
+        <v>2559</v>
       </c>
       <c r="G646" s="8" t="n">
-        <v>116</v>
+        <v>199</v>
       </c>
       <c r="H646" s="8" t="n">
-        <v>285</v>
+        <v>369.5</v>
       </c>
       <c r="I646" s="8" t="n">
-        <v>357.38</v>
+        <v>447.78</v>
       </c>
       <c r="J646" s="8" t="n">
-        <v>11654</v>
+        <v>8892</v>
       </c>
       <c r="K646" s="5" t="inlineStr">
         <is>
@@ -32694,29 +33491,29 @@
       </c>
       <c r="C647" s="5" t="inlineStr">
         <is>
-          <t>2026-10-11T00:00</t>
+          <t>2026-10-10T00:00</t>
         </is>
       </c>
       <c r="D647" s="6" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="E647" s="7" t="n">
-        <v>918</v>
+        <v>874</v>
       </c>
       <c r="F647" s="7" t="n">
-        <v>4008</v>
+        <v>3991</v>
       </c>
       <c r="G647" s="8" t="n">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="H647" s="8" t="n">
-        <v>264</v>
+        <v>285</v>
       </c>
       <c r="I647" s="8" t="n">
-        <v>304.98</v>
+        <v>357.38</v>
       </c>
       <c r="J647" s="8" t="n">
-        <v>4431</v>
+        <v>11654</v>
       </c>
       <c r="K647" s="5" t="inlineStr">
         <is>
@@ -32727,39 +33524,39 @@
     <row r="648">
       <c r="A648" s="5" t="inlineStr">
         <is>
-          <t>TBD at Atlanta Braves - NLCS (Home Game 2)</t>
+          <t>TBD at Tampa Bay Rays - ALCS (Game 1, Home Game 1)</t>
         </is>
       </c>
       <c r="B648" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13T07:30</t>
+          <t>2026-10-13T00:00</t>
         </is>
       </c>
       <c r="C648" s="5" t="inlineStr">
         <is>
-          <t>2026-09-29T01:45</t>
+          <t>2026-10-11T00:00</t>
         </is>
       </c>
       <c r="D648" s="6" t="n">
-        <v>341.7</v>
+        <v>48</v>
       </c>
       <c r="E648" s="7" t="n">
-        <v>724</v>
+        <v>918</v>
       </c>
       <c r="F648" s="7" t="n">
-        <v>4082</v>
+        <v>4008</v>
       </c>
       <c r="G648" s="8" t="n">
-        <v>155</v>
+        <v>99</v>
       </c>
       <c r="H648" s="8" t="n">
-        <v>357.5</v>
+        <v>264</v>
       </c>
       <c r="I648" s="8" t="n">
-        <v>505.02</v>
+        <v>304.98</v>
       </c>
       <c r="J648" s="8" t="n">
-        <v>9248</v>
+        <v>4431</v>
       </c>
       <c r="K648" s="5" t="inlineStr">
         <is>
@@ -32770,7 +33567,7 @@
     <row r="649">
       <c r="A649" s="5" t="inlineStr">
         <is>
-          <t>TBD at Boston Red Sox - ALCS (Home Game 2)</t>
+          <t>TBD at Atlanta Braves - NLCS (Home Game 2)</t>
         </is>
       </c>
       <c r="B649" s="5" t="inlineStr">
@@ -32787,22 +33584,22 @@
         <v>341.7</v>
       </c>
       <c r="E649" s="7" t="n">
-        <v>14</v>
+        <v>724</v>
       </c>
       <c r="F649" s="7" t="n">
-        <v>43</v>
+        <v>4082</v>
       </c>
       <c r="G649" s="8" t="n">
-        <v>703</v>
+        <v>155</v>
       </c>
       <c r="H649" s="8" t="n">
-        <v>1105.5</v>
+        <v>357.5</v>
       </c>
       <c r="I649" s="8" t="n">
-        <v>1512.07</v>
+        <v>505.02</v>
       </c>
       <c r="J649" s="8" t="n">
-        <v>4366</v>
+        <v>9248</v>
       </c>
       <c r="K649" s="5" t="inlineStr">
         <is>
@@ -32813,7 +33610,7 @@
     <row r="650">
       <c r="A650" s="5" t="inlineStr">
         <is>
-          <t>TBD at New York Yankees - ALCS (Home Game 2)</t>
+          <t>TBD at Boston Red Sox - ALCS (Home Game 2)</t>
         </is>
       </c>
       <c r="B650" s="5" t="inlineStr">
@@ -32830,22 +33627,22 @@
         <v>341.7</v>
       </c>
       <c r="E650" s="7" t="n">
-        <v>536</v>
+        <v>14</v>
       </c>
       <c r="F650" s="7" t="n">
-        <v>2575</v>
+        <v>43</v>
       </c>
       <c r="G650" s="8" t="n">
-        <v>207</v>
+        <v>703</v>
       </c>
       <c r="H650" s="8" t="n">
-        <v>493</v>
+        <v>1105.5</v>
       </c>
       <c r="I650" s="8" t="n">
-        <v>895.24</v>
+        <v>1512.07</v>
       </c>
       <c r="J650" s="8" t="n">
-        <v>11988</v>
+        <v>4366</v>
       </c>
       <c r="K650" s="5" t="inlineStr">
         <is>
@@ -32856,7 +33653,7 @@
     <row r="651">
       <c r="A651" s="5" t="inlineStr">
         <is>
-          <t>TBD at Philadelphia Phillies - NLCS (Home Game 1)</t>
+          <t>TBD at New York Yankees - ALCS (Home Game 2)</t>
         </is>
       </c>
       <c r="B651" s="5" t="inlineStr">
@@ -32873,22 +33670,22 @@
         <v>341.7</v>
       </c>
       <c r="E651" s="7" t="n">
-        <v>18</v>
+        <v>536</v>
       </c>
       <c r="F651" s="7" t="n">
-        <v>68</v>
+        <v>2575</v>
       </c>
       <c r="G651" s="8" t="n">
-        <v>633</v>
+        <v>207</v>
       </c>
       <c r="H651" s="8" t="n">
-        <v>1008</v>
+        <v>493</v>
       </c>
       <c r="I651" s="8" t="n">
-        <v>1468.11</v>
+        <v>895.24</v>
       </c>
       <c r="J651" s="8" t="n">
-        <v>4744</v>
+        <v>11988</v>
       </c>
       <c r="K651" s="5" t="inlineStr">
         <is>
@@ -32899,39 +33696,39 @@
     <row r="652">
       <c r="A652" s="5" t="inlineStr">
         <is>
-          <t>TBD at Chicago Cubs - NLCS (Home Game 1)</t>
+          <t>TBD at Philadelphia Phillies - NLCS (Home Game 1)</t>
         </is>
       </c>
       <c r="B652" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13T08:30</t>
+          <t>2026-10-13T07:30</t>
         </is>
       </c>
       <c r="C652" s="5" t="inlineStr">
         <is>
-          <t>2026-09-29T14:37</t>
+          <t>2026-09-29T01:45</t>
         </is>
       </c>
       <c r="D652" s="6" t="n">
-        <v>329.9</v>
+        <v>341.7</v>
       </c>
       <c r="E652" s="7" t="n">
-        <v>225</v>
+        <v>18</v>
       </c>
       <c r="F652" s="7" t="n">
-        <v>733</v>
+        <v>68</v>
       </c>
       <c r="G652" s="8" t="n">
-        <v>354</v>
+        <v>633</v>
       </c>
       <c r="H652" s="8" t="n">
-        <v>1263</v>
+        <v>1008</v>
       </c>
       <c r="I652" s="8" t="n">
-        <v>1984.95</v>
+        <v>1468.11</v>
       </c>
       <c r="J652" s="8" t="n">
-        <v>14436</v>
+        <v>4744</v>
       </c>
       <c r="K652" s="5" t="inlineStr">
         <is>
@@ -32942,7 +33739,7 @@
     <row r="653">
       <c r="A653" s="5" t="inlineStr">
         <is>
-          <t>TBD at Houston Astros - ALCS (Home Game 2)</t>
+          <t>TBD at Chicago Cubs - NLCS (Home Game 1)</t>
         </is>
       </c>
       <c r="B653" s="5" t="inlineStr">
@@ -32959,22 +33756,22 @@
         <v>329.9</v>
       </c>
       <c r="E653" s="7" t="n">
-        <v>18</v>
+        <v>225</v>
       </c>
       <c r="F653" s="7" t="n">
-        <v>68</v>
+        <v>733</v>
       </c>
       <c r="G653" s="8" t="n">
-        <v>262</v>
+        <v>354</v>
       </c>
       <c r="H653" s="8" t="n">
-        <v>326.5</v>
+        <v>1263</v>
       </c>
       <c r="I653" s="8" t="n">
-        <v>667.17</v>
+        <v>1984.95</v>
       </c>
       <c r="J653" s="8" t="n">
-        <v>2322</v>
+        <v>14436</v>
       </c>
       <c r="K653" s="5" t="inlineStr">
         <is>
@@ -32985,39 +33782,39 @@
     <row r="654">
       <c r="A654" s="5" t="inlineStr">
         <is>
-          <t>Cleveland Guardians at Tampa Bay Rays - ALCS (Game 2, Home Game 2)</t>
+          <t>TBD at Houston Astros - ALCS (Home Game 2)</t>
         </is>
       </c>
       <c r="B654" s="5" t="inlineStr">
         <is>
-          <t>2026-10-14T00:00</t>
+          <t>2026-10-13T08:30</t>
         </is>
       </c>
       <c r="C654" s="5" t="inlineStr">
         <is>
-          <t>2026-10-12T00:00</t>
+          <t>2026-09-29T14:37</t>
         </is>
       </c>
       <c r="D654" s="6" t="n">
-        <v>48</v>
+        <v>329.9</v>
       </c>
       <c r="E654" s="7" t="n">
-        <v>744</v>
+        <v>18</v>
       </c>
       <c r="F654" s="7" t="n">
-        <v>3173</v>
+        <v>68</v>
       </c>
       <c r="G654" s="8" t="n">
-        <v>95</v>
+        <v>262</v>
       </c>
       <c r="H654" s="8" t="n">
-        <v>258</v>
+        <v>326.5</v>
       </c>
       <c r="I654" s="8" t="n">
-        <v>303.84</v>
+        <v>667.17</v>
       </c>
       <c r="J654" s="8" t="n">
-        <v>11654</v>
+        <v>2322</v>
       </c>
       <c r="K654" s="5" t="inlineStr">
         <is>
@@ -33028,7 +33825,7 @@
     <row r="655">
       <c r="A655" s="5" t="inlineStr">
         <is>
-          <t>TBD at Tampa Bay Rays - ALCS (Game 2, Home Game 2)</t>
+          <t>Cleveland Guardians at Tampa Bay Rays - ALCS (Game 2, Home Game 2)</t>
         </is>
       </c>
       <c r="B655" s="5" t="inlineStr">
@@ -33038,29 +33835,29 @@
       </c>
       <c r="C655" s="5" t="inlineStr">
         <is>
-          <t>2026-09-29T01:45</t>
+          <t>2026-10-12T00:00</t>
         </is>
       </c>
       <c r="D655" s="6" t="n">
-        <v>358.2</v>
+        <v>48</v>
       </c>
       <c r="E655" s="7" t="n">
-        <v>394</v>
+        <v>744</v>
       </c>
       <c r="F655" s="7" t="n">
-        <v>2493</v>
+        <v>3173</v>
       </c>
       <c r="G655" s="8" t="n">
-        <v>194</v>
+        <v>95</v>
       </c>
       <c r="H655" s="8" t="n">
-        <v>365</v>
+        <v>258</v>
       </c>
       <c r="I655" s="8" t="n">
-        <v>452.79</v>
+        <v>303.84</v>
       </c>
       <c r="J655" s="8" t="n">
-        <v>8892</v>
+        <v>11654</v>
       </c>
       <c r="K655" s="5" t="inlineStr">
         <is>
@@ -33071,7 +33868,7 @@
     <row r="656">
       <c r="A656" s="5" t="inlineStr">
         <is>
-          <t>TBD at Tampa Bay Rays - ALCS (Game 2, Home Game 2)</t>
+          <t>Cleveland Guardians at Tampa Bay Rays - ALCS (Game 2, Home Game 2)</t>
         </is>
       </c>
       <c r="B656" s="5" t="inlineStr">
@@ -33081,29 +33878,29 @@
       </c>
       <c r="C656" s="5" t="inlineStr">
         <is>
-          <t>2026-10-11T00:00</t>
+          <t>2026-10-13T00:00</t>
         </is>
       </c>
       <c r="D656" s="6" t="n">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="E656" s="7" t="n">
-        <v>966</v>
+        <v>640</v>
       </c>
       <c r="F656" s="7" t="n">
-        <v>4500</v>
+        <v>2519</v>
       </c>
       <c r="G656" s="8" t="n">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="H656" s="8" t="n">
-        <v>298.5</v>
+        <v>215</v>
       </c>
       <c r="I656" s="8" t="n">
-        <v>319.93</v>
+        <v>246.45</v>
       </c>
       <c r="J656" s="8" t="n">
-        <v>4545</v>
+        <v>3977</v>
       </c>
       <c r="K656" s="5" t="inlineStr">
         <is>
@@ -33114,39 +33911,39 @@
     <row r="657">
       <c r="A657" s="5" t="inlineStr">
         <is>
-          <t>TBD at Philadelphia Phillies - NLCS (Home Game 2)</t>
+          <t>Cleveland Guardians at Tampa Bay Rays - ALCS (Game 2, Home Game 2)</t>
         </is>
       </c>
       <c r="B657" s="5" t="inlineStr">
         <is>
-          <t>2026-10-14T07:30</t>
+          <t>2026-10-14T00:00</t>
         </is>
       </c>
       <c r="C657" s="5" t="inlineStr">
         <is>
-          <t>2026-10-01T04:00</t>
+          <t>2026-10-13T18:00</t>
         </is>
       </c>
       <c r="D657" s="6" t="n">
-        <v>315.5</v>
+        <v>6</v>
       </c>
       <c r="E657" s="7" t="n">
-        <v>33</v>
+        <v>530</v>
       </c>
       <c r="F657" s="7" t="n">
-        <v>122</v>
+        <v>2098</v>
       </c>
       <c r="G657" s="8" t="n">
-        <v>633</v>
+        <v>90</v>
       </c>
       <c r="H657" s="8" t="n">
-        <v>2237</v>
+        <v>195.5</v>
       </c>
       <c r="I657" s="8" t="n">
-        <v>2218.42</v>
+        <v>226.95</v>
       </c>
       <c r="J657" s="8" t="n">
-        <v>5929</v>
+        <v>5680</v>
       </c>
       <c r="K657" s="5" t="inlineStr">
         <is>
@@ -33157,39 +33954,39 @@
     <row r="658">
       <c r="A658" s="5" t="inlineStr">
         <is>
-          <t>TBD at Chicago Cubs - NLCS (Home Game 2)</t>
+          <t>Cleveland Guardians at Tampa Bay Rays - ALCS (Game 2, Home Game 2)</t>
         </is>
       </c>
       <c r="B658" s="5" t="inlineStr">
         <is>
-          <t>2026-10-14T08:30</t>
+          <t>2026-10-14T00:00</t>
         </is>
       </c>
       <c r="C658" s="5" t="inlineStr">
         <is>
-          <t>2026-10-01T05:00</t>
+          <t>2026-10-13T21:00</t>
         </is>
       </c>
       <c r="D658" s="6" t="n">
-        <v>315.5</v>
+        <v>3</v>
       </c>
       <c r="E658" s="7" t="n">
-        <v>240</v>
+        <v>452</v>
       </c>
       <c r="F658" s="7" t="n">
-        <v>774</v>
+        <v>1723</v>
       </c>
       <c r="G658" s="8" t="n">
-        <v>392</v>
+        <v>79</v>
       </c>
       <c r="H658" s="8" t="n">
-        <v>1255</v>
+        <v>175</v>
       </c>
       <c r="I658" s="8" t="n">
-        <v>1914.46</v>
+        <v>215.7</v>
       </c>
       <c r="J658" s="8" t="n">
-        <v>10669</v>
+        <v>5680</v>
       </c>
       <c r="K658" s="5" t="inlineStr">
         <is>
@@ -33200,39 +33997,39 @@
     <row r="659">
       <c r="A659" s="5" t="inlineStr">
         <is>
-          <t>TBD at San Diego Padres - NLCS (Home Game 1)</t>
+          <t>Cleveland Guardians at Tampa Bay Rays - ALCS (Game 2, Home Game 2)</t>
         </is>
       </c>
       <c r="B659" s="5" t="inlineStr">
         <is>
-          <t>2026-10-14T10:30</t>
+          <t>2026-10-14T00:00</t>
         </is>
       </c>
       <c r="C659" s="5" t="inlineStr">
         <is>
-          <t>2026-10-01T04:00</t>
+          <t>2026-10-13T23:00</t>
         </is>
       </c>
       <c r="D659" s="6" t="n">
-        <v>318.5</v>
+        <v>1</v>
       </c>
       <c r="E659" s="7" t="n">
-        <v>42</v>
+        <v>319</v>
       </c>
       <c r="F659" s="7" t="n">
-        <v>138</v>
+        <v>1295</v>
       </c>
       <c r="G659" s="8" t="n">
-        <v>283</v>
+        <v>69</v>
       </c>
       <c r="H659" s="8" t="n">
-        <v>1118.5</v>
+        <v>141</v>
       </c>
       <c r="I659" s="8" t="n">
-        <v>1800.62</v>
+        <v>200.34</v>
       </c>
       <c r="J659" s="8" t="n">
-        <v>4745</v>
+        <v>5680</v>
       </c>
       <c r="K659" s="5" t="inlineStr">
         <is>
@@ -33243,39 +34040,39 @@
     <row r="660">
       <c r="A660" s="5" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers at Los Angeles Dodgers - NLCS (Game 3, Home Game 1)</t>
+          <t>TBD at Tampa Bay Rays - ALCS (Game 2, Home Game 2)</t>
         </is>
       </c>
       <c r="B660" s="5" t="inlineStr">
         <is>
-          <t>2026-10-15T00:00</t>
+          <t>2026-10-14T00:00</t>
         </is>
       </c>
       <c r="C660" s="5" t="inlineStr">
         <is>
-          <t>2026-10-12T00:00</t>
+          <t>2026-09-29T01:45</t>
         </is>
       </c>
       <c r="D660" s="6" t="n">
-        <v>72</v>
+        <v>358.2</v>
       </c>
       <c r="E660" s="7" t="n">
-        <v>1912</v>
+        <v>394</v>
       </c>
       <c r="F660" s="7" t="n">
-        <v>8019</v>
+        <v>2493</v>
       </c>
       <c r="G660" s="8" t="n">
-        <v>154</v>
+        <v>194</v>
       </c>
       <c r="H660" s="8" t="n">
-        <v>248</v>
+        <v>365</v>
       </c>
       <c r="I660" s="8" t="n">
-        <v>425.71</v>
+        <v>452.79</v>
       </c>
       <c r="J660" s="8" t="n">
-        <v>16431</v>
+        <v>8892</v>
       </c>
       <c r="K660" s="5" t="inlineStr">
         <is>
@@ -33286,39 +34083,39 @@
     <row r="661">
       <c r="A661" s="5" t="inlineStr">
         <is>
-          <t>TBD at Los Angeles Dodgers - NLCS (Home Game 1)</t>
+          <t>TBD at Tampa Bay Rays - ALCS (Game 2, Home Game 2)</t>
         </is>
       </c>
       <c r="B661" s="5" t="inlineStr">
         <is>
-          <t>2026-10-15T00:00</t>
+          <t>2026-10-14T00:00</t>
         </is>
       </c>
       <c r="C661" s="5" t="inlineStr">
         <is>
-          <t>2026-10-01T04:00</t>
+          <t>2026-10-11T00:00</t>
         </is>
       </c>
       <c r="D661" s="6" t="n">
-        <v>332</v>
+        <v>72</v>
       </c>
       <c r="E661" s="7" t="n">
-        <v>2012</v>
+        <v>966</v>
       </c>
       <c r="F661" s="7" t="n">
-        <v>9938</v>
+        <v>4500</v>
       </c>
       <c r="G661" s="8" t="n">
-        <v>190</v>
+        <v>107</v>
       </c>
       <c r="H661" s="8" t="n">
-        <v>322</v>
+        <v>298.5</v>
       </c>
       <c r="I661" s="8" t="n">
-        <v>534.8099999999999</v>
+        <v>319.93</v>
       </c>
       <c r="J661" s="8" t="n">
-        <v>20521</v>
+        <v>4545</v>
       </c>
       <c r="K661" s="5" t="inlineStr">
         <is>
@@ -33329,36 +34126,36 @@
     <row r="662">
       <c r="A662" s="5" t="inlineStr">
         <is>
-          <t>TBD at San Diego Padres - NLCS (Home Game 2)</t>
+          <t>TBD at Philadelphia Phillies - NLCS (Home Game 2)</t>
         </is>
       </c>
       <c r="B662" s="5" t="inlineStr">
         <is>
-          <t>2026-10-15T10:30</t>
+          <t>2026-10-14T07:30</t>
         </is>
       </c>
       <c r="C662" s="5" t="inlineStr">
         <is>
-          <t>2026-10-01T05:00</t>
+          <t>2026-10-01T04:00</t>
         </is>
       </c>
       <c r="D662" s="6" t="n">
-        <v>341.5</v>
+        <v>315.5</v>
       </c>
       <c r="E662" s="7" t="n">
-        <v>791</v>
+        <v>33</v>
       </c>
       <c r="F662" s="7" t="n">
-        <v>3949</v>
+        <v>122</v>
       </c>
       <c r="G662" s="8" t="n">
-        <v>289</v>
+        <v>633</v>
       </c>
       <c r="H662" s="8" t="n">
-        <v>520</v>
+        <v>2237</v>
       </c>
       <c r="I662" s="8" t="n">
-        <v>621.71</v>
+        <v>2218.42</v>
       </c>
       <c r="J662" s="8" t="n">
         <v>5929</v>
@@ -33372,39 +34169,39 @@
     <row r="663">
       <c r="A663" s="5" t="inlineStr">
         <is>
-          <t>TBD at Chicago White Sox - ALCS (Game 3, Home Game 1)</t>
+          <t>TBD at Chicago Cubs - NLCS (Home Game 2)</t>
         </is>
       </c>
       <c r="B663" s="5" t="inlineStr">
         <is>
-          <t>2026-10-15T22:00</t>
+          <t>2026-10-14T08:30</t>
         </is>
       </c>
       <c r="C663" s="5" t="inlineStr">
         <is>
-          <t>2026-09-29T01:45</t>
+          <t>2026-10-01T05:00</t>
         </is>
       </c>
       <c r="D663" s="6" t="n">
-        <v>404.2</v>
+        <v>315.5</v>
       </c>
       <c r="E663" s="7" t="n">
-        <v>287</v>
+        <v>240</v>
       </c>
       <c r="F663" s="7" t="n">
-        <v>1238</v>
+        <v>774</v>
       </c>
       <c r="G663" s="8" t="n">
-        <v>177</v>
+        <v>392</v>
       </c>
       <c r="H663" s="8" t="n">
-        <v>449</v>
+        <v>1255</v>
       </c>
       <c r="I663" s="8" t="n">
-        <v>623.28</v>
+        <v>1914.46</v>
       </c>
       <c r="J663" s="8" t="n">
-        <v>11855</v>
+        <v>10669</v>
       </c>
       <c r="K663" s="5" t="inlineStr">
         <is>
@@ -33415,39 +34212,39 @@
     <row r="664">
       <c r="A664" s="5" t="inlineStr">
         <is>
-          <t>TBD at Cleveland Guardians - ALCS (Home Game 1)</t>
+          <t>TBD at San Diego Padres - NLCS (Home Game 1)</t>
         </is>
       </c>
       <c r="B664" s="5" t="inlineStr">
         <is>
-          <t>2026-10-15T22:00</t>
+          <t>2026-10-14T10:30</t>
         </is>
       </c>
       <c r="C664" s="5" t="inlineStr">
         <is>
-          <t>2026-09-29T01:45</t>
+          <t>2026-10-01T04:00</t>
         </is>
       </c>
       <c r="D664" s="6" t="n">
-        <v>404.2</v>
+        <v>318.5</v>
       </c>
       <c r="E664" s="7" t="n">
-        <v>531</v>
+        <v>42</v>
       </c>
       <c r="F664" s="7" t="n">
-        <v>2597</v>
+        <v>138</v>
       </c>
       <c r="G664" s="8" t="n">
-        <v>262</v>
+        <v>283</v>
       </c>
       <c r="H664" s="8" t="n">
-        <v>474</v>
+        <v>1118.5</v>
       </c>
       <c r="I664" s="8" t="n">
-        <v>492.1</v>
+        <v>1800.62</v>
       </c>
       <c r="J664" s="8" t="n">
-        <v>1673</v>
+        <v>4745</v>
       </c>
       <c r="K664" s="5" t="inlineStr">
         <is>
@@ -33458,39 +34255,39 @@
     <row r="665">
       <c r="A665" s="5" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays at Cleveland Guardians - ALCS (Game 3, Home Game 1)</t>
+          <t>Milwaukee Brewers at Los Angeles Dodgers - NLCS (Game 3, Home Game 1)</t>
         </is>
       </c>
       <c r="B665" s="5" t="inlineStr">
         <is>
-          <t>2026-10-15T22:00</t>
+          <t>2026-10-15T00:00</t>
         </is>
       </c>
       <c r="C665" s="5" t="inlineStr">
         <is>
-          <t>2026-10-12T22:00</t>
+          <t>2026-10-12T00:00</t>
         </is>
       </c>
       <c r="D665" s="6" t="n">
         <v>72</v>
       </c>
       <c r="E665" s="7" t="n">
-        <v>690</v>
+        <v>1912</v>
       </c>
       <c r="F665" s="7" t="n">
-        <v>2648</v>
+        <v>8019</v>
       </c>
       <c r="G665" s="8" t="n">
-        <v>221</v>
+        <v>154</v>
       </c>
       <c r="H665" s="8" t="n">
-        <v>403</v>
+        <v>248</v>
       </c>
       <c r="I665" s="8" t="n">
-        <v>450.19</v>
+        <v>425.71</v>
       </c>
       <c r="J665" s="8" t="n">
-        <v>2218</v>
+        <v>16431</v>
       </c>
       <c r="K665" s="5" t="inlineStr">
         <is>
@@ -33501,39 +34298,39 @@
     <row r="666">
       <c r="A666" s="5" t="inlineStr">
         <is>
-          <t>TBD at Los Angeles Dodgers - NLCS (Home Game 2)</t>
+          <t>Milwaukee Brewers at Los Angeles Dodgers - NLCS (Game 3, Home Game 1)</t>
         </is>
       </c>
       <c r="B666" s="5" t="inlineStr">
         <is>
-          <t>2026-10-16T01:00</t>
+          <t>2026-10-15T00:00</t>
         </is>
       </c>
       <c r="C666" s="5" t="inlineStr">
         <is>
-          <t>2026-10-01T05:00</t>
+          <t>2026-10-13T00:00</t>
         </is>
       </c>
       <c r="D666" s="6" t="n">
-        <v>356</v>
+        <v>48</v>
       </c>
       <c r="E666" s="7" t="n">
-        <v>1987</v>
+        <v>1945</v>
       </c>
       <c r="F666" s="7" t="n">
-        <v>9878</v>
+        <v>8153</v>
       </c>
       <c r="G666" s="8" t="n">
-        <v>174</v>
+        <v>141</v>
       </c>
       <c r="H666" s="8" t="n">
-        <v>276</v>
+        <v>223</v>
       </c>
       <c r="I666" s="8" t="n">
-        <v>503.42</v>
+        <v>386.54</v>
       </c>
       <c r="J666" s="8" t="n">
-        <v>20521</v>
+        <v>13694</v>
       </c>
       <c r="K666" s="5" t="inlineStr">
         <is>
@@ -33544,39 +34341,39 @@
     <row r="667">
       <c r="A667" s="5" t="inlineStr">
         <is>
-          <t>TBD at Chicago White Sox - ALCS (Game 4, Home Game 2)</t>
+          <t>Milwaukee Brewers at Los Angeles Dodgers - NLCS (Game 3, Home Game 1)</t>
         </is>
       </c>
       <c r="B667" s="5" t="inlineStr">
         <is>
-          <t>2026-10-16T22:00</t>
+          <t>2026-10-15T00:00</t>
         </is>
       </c>
       <c r="C667" s="5" t="inlineStr">
         <is>
-          <t>2026-10-01T03:00</t>
+          <t>2026-10-14T00:00</t>
         </is>
       </c>
       <c r="D667" s="6" t="n">
-        <v>379</v>
+        <v>24</v>
       </c>
       <c r="E667" s="7" t="n">
-        <v>265</v>
+        <v>1643</v>
       </c>
       <c r="F667" s="7" t="n">
-        <v>1230</v>
+        <v>6607</v>
       </c>
       <c r="G667" s="8" t="n">
-        <v>245</v>
+        <v>90</v>
       </c>
       <c r="H667" s="8" t="n">
-        <v>531</v>
+        <v>163</v>
       </c>
       <c r="I667" s="8" t="n">
-        <v>903.11</v>
+        <v>290.07</v>
       </c>
       <c r="J667" s="8" t="n">
-        <v>13040</v>
+        <v>10408</v>
       </c>
       <c r="K667" s="5" t="inlineStr">
         <is>
@@ -33587,39 +34384,39 @@
     <row r="668">
       <c r="A668" s="5" t="inlineStr">
         <is>
-          <t>TBD at Cleveland Guardians - ALCS (Home Game 2)</t>
+          <t>Milwaukee Brewers at Los Angeles Dodgers - NLCS (Game 3, Home Game 1)</t>
         </is>
       </c>
       <c r="B668" s="5" t="inlineStr">
         <is>
-          <t>2026-10-16T22:00</t>
+          <t>2026-10-15T00:00</t>
         </is>
       </c>
       <c r="C668" s="5" t="inlineStr">
         <is>
-          <t>2026-09-29T14:37</t>
+          <t>2026-10-14T12:00</t>
         </is>
       </c>
       <c r="D668" s="6" t="n">
-        <v>415.4</v>
+        <v>12</v>
       </c>
       <c r="E668" s="7" t="n">
-        <v>534</v>
+        <v>1711</v>
       </c>
       <c r="F668" s="7" t="n">
-        <v>2619</v>
+        <v>8309</v>
       </c>
       <c r="G668" s="8" t="n">
-        <v>241</v>
+        <v>94</v>
       </c>
       <c r="H668" s="8" t="n">
-        <v>473</v>
+        <v>232</v>
       </c>
       <c r="I668" s="8" t="n">
-        <v>493.45</v>
+        <v>307.23</v>
       </c>
       <c r="J668" s="8" t="n">
-        <v>1657</v>
+        <v>10408</v>
       </c>
       <c r="K668" s="5" t="inlineStr">
         <is>
@@ -33630,39 +34427,39 @@
     <row r="669">
       <c r="A669" s="5" t="inlineStr">
         <is>
-          <t>TBD at Atlanta Braves - NLCS (Home Game 3)</t>
+          <t>Milwaukee Brewers at Los Angeles Dodgers - NLCS (Game 3, Home Game 1)</t>
         </is>
       </c>
       <c r="B669" s="5" t="inlineStr">
         <is>
-          <t>2026-10-17T07:30</t>
+          <t>2026-10-15T00:00</t>
         </is>
       </c>
       <c r="C669" s="5" t="inlineStr">
         <is>
-          <t>2026-10-01T06:00</t>
+          <t>2026-10-14T18:00</t>
         </is>
       </c>
       <c r="D669" s="6" t="n">
-        <v>385.5</v>
+        <v>6</v>
       </c>
       <c r="E669" s="7" t="n">
-        <v>838</v>
+        <v>1105</v>
       </c>
       <c r="F669" s="7" t="n">
-        <v>4757</v>
+        <v>4252</v>
       </c>
       <c r="G669" s="8" t="n">
-        <v>201</v>
+        <v>94</v>
       </c>
       <c r="H669" s="8" t="n">
-        <v>446</v>
+        <v>138</v>
       </c>
       <c r="I669" s="8" t="n">
-        <v>802.95</v>
+        <v>260.6</v>
       </c>
       <c r="J669" s="8" t="n">
-        <v>17780</v>
+        <v>4999</v>
       </c>
       <c r="K669" s="5" t="inlineStr">
         <is>
@@ -33673,39 +34470,39 @@
     <row r="670">
       <c r="A670" s="5" t="inlineStr">
         <is>
-          <t>TBD at New York Yankees - ALCS (Home Game 3)</t>
+          <t>Milwaukee Brewers at Los Angeles Dodgers - NLCS (Game 3, Home Game 1)</t>
         </is>
       </c>
       <c r="B670" s="5" t="inlineStr">
         <is>
-          <t>2026-10-17T07:30</t>
+          <t>2026-10-15T00:00</t>
         </is>
       </c>
       <c r="C670" s="5" t="inlineStr">
         <is>
-          <t>2026-10-01T06:00</t>
+          <t>2026-10-14T21:00</t>
         </is>
       </c>
       <c r="D670" s="6" t="n">
-        <v>385.5</v>
+        <v>3</v>
       </c>
       <c r="E670" s="7" t="n">
-        <v>576</v>
+        <v>796</v>
       </c>
       <c r="F670" s="7" t="n">
-        <v>2522</v>
+        <v>2971</v>
       </c>
       <c r="G670" s="8" t="n">
-        <v>246</v>
+        <v>62</v>
       </c>
       <c r="H670" s="8" t="n">
-        <v>623</v>
+        <v>125</v>
       </c>
       <c r="I670" s="8" t="n">
-        <v>1182.05</v>
+        <v>224.79</v>
       </c>
       <c r="J670" s="8" t="n">
-        <v>11988</v>
+        <v>4999</v>
       </c>
       <c r="K670" s="5" t="inlineStr">
         <is>
@@ -33716,39 +34513,39 @@
     <row r="671">
       <c r="A671" s="5" t="inlineStr">
         <is>
-          <t>TBD at Chicago White Sox - ALCS (Game 5, Home Game 3)</t>
+          <t>Milwaukee Brewers at Los Angeles Dodgers - NLCS (Game 3, Home Game 1)</t>
         </is>
       </c>
       <c r="B671" s="5" t="inlineStr">
         <is>
-          <t>2026-10-18T00:00</t>
+          <t>2026-10-15T00:00</t>
         </is>
       </c>
       <c r="C671" s="5" t="inlineStr">
         <is>
-          <t>2026-10-01T07:00</t>
+          <t>2026-10-14T23:00</t>
         </is>
       </c>
       <c r="D671" s="6" t="n">
-        <v>401</v>
+        <v>1</v>
       </c>
       <c r="E671" s="7" t="n">
-        <v>175</v>
+        <v>603</v>
       </c>
       <c r="F671" s="7" t="n">
-        <v>829</v>
+        <v>2223</v>
       </c>
       <c r="G671" s="8" t="n">
-        <v>245</v>
+        <v>95</v>
       </c>
       <c r="H671" s="8" t="n">
-        <v>530</v>
+        <v>112</v>
       </c>
       <c r="I671" s="8" t="n">
-        <v>939.5700000000001</v>
+        <v>210.7</v>
       </c>
       <c r="J671" s="8" t="n">
-        <v>14225</v>
+        <v>4999</v>
       </c>
       <c r="K671" s="5" t="inlineStr">
         <is>
@@ -33759,41 +34556,2879 @@
     <row r="672">
       <c r="A672" s="5" t="inlineStr">
         <is>
+          <t>TBD at Los Angeles Dodgers - NLCS (Home Game 1)</t>
+        </is>
+      </c>
+      <c r="B672" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-15T00:00</t>
+        </is>
+      </c>
+      <c r="C672" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-01T04:00</t>
+        </is>
+      </c>
+      <c r="D672" s="6" t="n">
+        <v>332</v>
+      </c>
+      <c r="E672" s="7" t="n">
+        <v>2012</v>
+      </c>
+      <c r="F672" s="7" t="n">
+        <v>9938</v>
+      </c>
+      <c r="G672" s="8" t="n">
+        <v>190</v>
+      </c>
+      <c r="H672" s="8" t="n">
+        <v>322</v>
+      </c>
+      <c r="I672" s="8" t="n">
+        <v>534.8099999999999</v>
+      </c>
+      <c r="J672" s="8" t="n">
+        <v>20521</v>
+      </c>
+      <c r="K672" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" s="5" t="inlineStr">
+        <is>
+          <t>TBD at San Diego Padres - NLCS (Home Game 2)</t>
+        </is>
+      </c>
+      <c r="B673" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-15T10:30</t>
+        </is>
+      </c>
+      <c r="C673" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-01T05:00</t>
+        </is>
+      </c>
+      <c r="D673" s="6" t="n">
+        <v>341.5</v>
+      </c>
+      <c r="E673" s="7" t="n">
+        <v>791</v>
+      </c>
+      <c r="F673" s="7" t="n">
+        <v>3949</v>
+      </c>
+      <c r="G673" s="8" t="n">
+        <v>289</v>
+      </c>
+      <c r="H673" s="8" t="n">
+        <v>520</v>
+      </c>
+      <c r="I673" s="8" t="n">
+        <v>621.71</v>
+      </c>
+      <c r="J673" s="8" t="n">
+        <v>5929</v>
+      </c>
+      <c r="K673" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" s="5" t="inlineStr">
+        <is>
+          <t>TBD at Chicago White Sox - ALCS (Game 3, Home Game 1)</t>
+        </is>
+      </c>
+      <c r="B674" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-15T22:00</t>
+        </is>
+      </c>
+      <c r="C674" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-29T01:45</t>
+        </is>
+      </c>
+      <c r="D674" s="6" t="n">
+        <v>404.2</v>
+      </c>
+      <c r="E674" s="7" t="n">
+        <v>287</v>
+      </c>
+      <c r="F674" s="7" t="n">
+        <v>1238</v>
+      </c>
+      <c r="G674" s="8" t="n">
+        <v>177</v>
+      </c>
+      <c r="H674" s="8" t="n">
+        <v>449</v>
+      </c>
+      <c r="I674" s="8" t="n">
+        <v>623.28</v>
+      </c>
+      <c r="J674" s="8" t="n">
+        <v>11855</v>
+      </c>
+      <c r="K674" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" s="5" t="inlineStr">
+        <is>
+          <t>TBD at Cleveland Guardians - ALCS (Home Game 1)</t>
+        </is>
+      </c>
+      <c r="B675" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-15T22:00</t>
+        </is>
+      </c>
+      <c r="C675" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-29T01:45</t>
+        </is>
+      </c>
+      <c r="D675" s="6" t="n">
+        <v>404.2</v>
+      </c>
+      <c r="E675" s="7" t="n">
+        <v>531</v>
+      </c>
+      <c r="F675" s="7" t="n">
+        <v>2597</v>
+      </c>
+      <c r="G675" s="8" t="n">
+        <v>262</v>
+      </c>
+      <c r="H675" s="8" t="n">
+        <v>474</v>
+      </c>
+      <c r="I675" s="8" t="n">
+        <v>492.1</v>
+      </c>
+      <c r="J675" s="8" t="n">
+        <v>1673</v>
+      </c>
+      <c r="K675" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" s="5" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays at Cleveland Guardians - ALCS (Game 3, Home Game 1)</t>
+        </is>
+      </c>
+      <c r="B676" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-15T22:00</t>
+        </is>
+      </c>
+      <c r="C676" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-12T22:00</t>
+        </is>
+      </c>
+      <c r="D676" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="E676" s="7" t="n">
+        <v>690</v>
+      </c>
+      <c r="F676" s="7" t="n">
+        <v>2648</v>
+      </c>
+      <c r="G676" s="8" t="n">
+        <v>221</v>
+      </c>
+      <c r="H676" s="8" t="n">
+        <v>403</v>
+      </c>
+      <c r="I676" s="8" t="n">
+        <v>450.19</v>
+      </c>
+      <c r="J676" s="8" t="n">
+        <v>2218</v>
+      </c>
+      <c r="K676" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" s="5" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays at Cleveland Guardians - ALCS (Game 3, Home Game 1)</t>
+        </is>
+      </c>
+      <c r="B677" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-15T22:00</t>
+        </is>
+      </c>
+      <c r="C677" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-13T22:00</t>
+        </is>
+      </c>
+      <c r="D677" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="E677" s="7" t="n">
+        <v>1126</v>
+      </c>
+      <c r="F677" s="7" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G677" s="8" t="n">
+        <v>170</v>
+      </c>
+      <c r="H677" s="8" t="n">
+        <v>317</v>
+      </c>
+      <c r="I677" s="8" t="n">
+        <v>351.52</v>
+      </c>
+      <c r="J677" s="8" t="n">
+        <v>2218</v>
+      </c>
+      <c r="K677" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="5" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays at Cleveland Guardians - ALCS (Game 3, Home Game 1)</t>
+        </is>
+      </c>
+      <c r="B678" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-15T22:00</t>
+        </is>
+      </c>
+      <c r="C678" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-14T17:00</t>
+        </is>
+      </c>
+      <c r="D678" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="E678" s="7" t="n">
+        <v>876</v>
+      </c>
+      <c r="F678" s="7" t="n">
+        <v>3224</v>
+      </c>
+      <c r="G678" s="8" t="n">
+        <v>105</v>
+      </c>
+      <c r="H678" s="8" t="n">
+        <v>230.5</v>
+      </c>
+      <c r="I678" s="8" t="n">
+        <v>265.46</v>
+      </c>
+      <c r="J678" s="8" t="n">
+        <v>2218</v>
+      </c>
+      <c r="K678" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" s="5" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays at Cleveland Guardians - ALCS (Game 3, Home Game 1)</t>
+        </is>
+      </c>
+      <c r="B679" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-15T22:00</t>
+        </is>
+      </c>
+      <c r="C679" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-15T05:00</t>
+        </is>
+      </c>
+      <c r="D679" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="E679" s="7" t="n">
+        <v>799</v>
+      </c>
+      <c r="F679" s="7" t="n">
+        <v>2788</v>
+      </c>
+      <c r="G679" s="8" t="n">
+        <v>105</v>
+      </c>
+      <c r="H679" s="8" t="n">
+        <v>187</v>
+      </c>
+      <c r="I679" s="8" t="n">
+        <v>241.3</v>
+      </c>
+      <c r="J679" s="8" t="n">
+        <v>9085</v>
+      </c>
+      <c r="K679" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" s="5" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays at Cleveland Guardians - ALCS (Game 3, Home Game 1)</t>
+        </is>
+      </c>
+      <c r="B680" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-15T22:00</t>
+        </is>
+      </c>
+      <c r="C680" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-15T11:00</t>
+        </is>
+      </c>
+      <c r="D680" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="E680" s="7" t="n">
+        <v>760</v>
+      </c>
+      <c r="F680" s="7" t="n">
+        <v>2663</v>
+      </c>
+      <c r="G680" s="8" t="n">
+        <v>101</v>
+      </c>
+      <c r="H680" s="8" t="n">
+        <v>188</v>
+      </c>
+      <c r="I680" s="8" t="n">
+        <v>242.36</v>
+      </c>
+      <c r="J680" s="8" t="n">
+        <v>9085</v>
+      </c>
+      <c r="K680" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" s="5" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays at Cleveland Guardians - ALCS (Game 3, Home Game 1)</t>
+        </is>
+      </c>
+      <c r="B681" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-15T22:00</t>
+        </is>
+      </c>
+      <c r="C681" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-15T14:00</t>
+        </is>
+      </c>
+      <c r="D681" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E681" s="7" t="n">
+        <v>529</v>
+      </c>
+      <c r="F681" s="7" t="n">
+        <v>1924</v>
+      </c>
+      <c r="G681" s="8" t="n">
+        <v>90</v>
+      </c>
+      <c r="H681" s="8" t="n">
+        <v>165</v>
+      </c>
+      <c r="I681" s="8" t="n">
+        <v>209.1</v>
+      </c>
+      <c r="J681" s="8" t="n">
+        <v>1253</v>
+      </c>
+      <c r="K681" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" s="5" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays at Cleveland Guardians - ALCS (Game 3, Home Game 1)</t>
+        </is>
+      </c>
+      <c r="B682" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-15T22:00</t>
+        </is>
+      </c>
+      <c r="C682" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-15T16:00</t>
+        </is>
+      </c>
+      <c r="D682" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E682" s="7" t="n">
+        <v>263</v>
+      </c>
+      <c r="F682" s="7" t="n">
+        <v>1065</v>
+      </c>
+      <c r="G682" s="8" t="n">
+        <v>106</v>
+      </c>
+      <c r="H682" s="8" t="n">
+        <v>155</v>
+      </c>
+      <c r="I682" s="8" t="n">
+        <v>210.48</v>
+      </c>
+      <c r="J682" s="8" t="n">
+        <v>1253</v>
+      </c>
+      <c r="K682" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" s="5" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers at Los Angeles Dodgers - NLCS (Game 4, Home Game 2)</t>
+        </is>
+      </c>
+      <c r="B683" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-16T01:00</t>
+        </is>
+      </c>
+      <c r="C683" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-13T01:00</t>
+        </is>
+      </c>
+      <c r="D683" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="E683" s="7" t="n">
+        <v>2368</v>
+      </c>
+      <c r="F683" s="7" t="n">
+        <v>10552</v>
+      </c>
+      <c r="G683" s="8" t="n">
+        <v>92</v>
+      </c>
+      <c r="H683" s="8" t="n">
+        <v>223</v>
+      </c>
+      <c r="I683" s="8" t="n">
+        <v>611.45</v>
+      </c>
+      <c r="J683" s="8" t="n">
+        <v>23287</v>
+      </c>
+      <c r="K683" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="5" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers at Los Angeles Dodgers - NLCS (Game 4, Home Game 2)</t>
+        </is>
+      </c>
+      <c r="B684" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-16T01:00</t>
+        </is>
+      </c>
+      <c r="C684" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-14T01:00</t>
+        </is>
+      </c>
+      <c r="D684" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="E684" s="7" t="n">
+        <v>1942</v>
+      </c>
+      <c r="F684" s="7" t="n">
+        <v>8258</v>
+      </c>
+      <c r="G684" s="8" t="n">
+        <v>94</v>
+      </c>
+      <c r="H684" s="8" t="n">
+        <v>184</v>
+      </c>
+      <c r="I684" s="8" t="n">
+        <v>475.54</v>
+      </c>
+      <c r="J684" s="8" t="n">
+        <v>16393</v>
+      </c>
+      <c r="K684" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" s="5" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers at Los Angeles Dodgers - NLCS (Game 4, Home Game 2)</t>
+        </is>
+      </c>
+      <c r="B685" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-16T01:00</t>
+        </is>
+      </c>
+      <c r="C685" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-15T00:00</t>
+        </is>
+      </c>
+      <c r="D685" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="E685" s="7" t="n">
+        <v>1481</v>
+      </c>
+      <c r="F685" s="7" t="n">
+        <v>5872</v>
+      </c>
+      <c r="G685" s="8" t="n">
+        <v>94</v>
+      </c>
+      <c r="H685" s="8" t="n">
+        <v>175</v>
+      </c>
+      <c r="I685" s="8" t="n">
+        <v>499.31</v>
+      </c>
+      <c r="J685" s="8" t="n">
+        <v>19147</v>
+      </c>
+      <c r="K685" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="5" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers at Los Angeles Dodgers - NLCS (Game 4, Home Game 2)</t>
+        </is>
+      </c>
+      <c r="B686" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-16T01:00</t>
+        </is>
+      </c>
+      <c r="C686" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-15T12:00</t>
+        </is>
+      </c>
+      <c r="D686" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="E686" s="7" t="n">
+        <v>1388</v>
+      </c>
+      <c r="F686" s="7" t="n">
+        <v>5130</v>
+      </c>
+      <c r="G686" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="H686" s="8" t="n">
+        <v>169</v>
+      </c>
+      <c r="I686" s="8" t="n">
+        <v>332.61</v>
+      </c>
+      <c r="J686" s="8" t="n">
+        <v>15884</v>
+      </c>
+      <c r="K686" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" s="5" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers at Los Angeles Dodgers - NLCS (Game 4, Home Game 2)</t>
+        </is>
+      </c>
+      <c r="B687" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-16T01:00</t>
+        </is>
+      </c>
+      <c r="C687" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-15T18:00</t>
+        </is>
+      </c>
+      <c r="D687" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E687" s="7" t="n">
+        <v>1140</v>
+      </c>
+      <c r="F687" s="7" t="n">
+        <v>3967</v>
+      </c>
+      <c r="G687" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="H687" s="8" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="I687" s="8" t="n">
+        <v>386.74</v>
+      </c>
+      <c r="J687" s="8" t="n">
+        <v>117669</v>
+      </c>
+      <c r="K687" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="5" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers at Los Angeles Dodgers - NLCS (Game 4, Home Game 2)</t>
+        </is>
+      </c>
+      <c r="B688" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-16T01:00</t>
+        </is>
+      </c>
+      <c r="C688" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-15T21:00</t>
+        </is>
+      </c>
+      <c r="D688" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E688" s="7" t="n">
+        <v>750</v>
+      </c>
+      <c r="F688" s="7" t="n">
+        <v>2466</v>
+      </c>
+      <c r="G688" s="8" t="n">
+        <v>77</v>
+      </c>
+      <c r="H688" s="8" t="n">
+        <v>118</v>
+      </c>
+      <c r="I688" s="8" t="n">
+        <v>270.52</v>
+      </c>
+      <c r="J688" s="8" t="n">
+        <v>6815</v>
+      </c>
+      <c r="K688" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" s="5" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers at Los Angeles Dodgers - NLCS (Game 4, Home Game 2)</t>
+        </is>
+      </c>
+      <c r="B689" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-16T01:00</t>
+        </is>
+      </c>
+      <c r="C689" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-15T23:00</t>
+        </is>
+      </c>
+      <c r="D689" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E689" s="7" t="n">
+        <v>541</v>
+      </c>
+      <c r="F689" s="7" t="n">
+        <v>1908</v>
+      </c>
+      <c r="G689" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="H689" s="8" t="n">
+        <v>101</v>
+      </c>
+      <c r="I689" s="8" t="n">
+        <v>226.68</v>
+      </c>
+      <c r="J689" s="8" t="n">
+        <v>4545</v>
+      </c>
+      <c r="K689" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" s="5" t="inlineStr">
+        <is>
+          <t>TBD at Los Angeles Dodgers - NLCS (Home Game 2)</t>
+        </is>
+      </c>
+      <c r="B690" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-16T01:00</t>
+        </is>
+      </c>
+      <c r="C690" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-01T05:00</t>
+        </is>
+      </c>
+      <c r="D690" s="6" t="n">
+        <v>356</v>
+      </c>
+      <c r="E690" s="7" t="n">
+        <v>1987</v>
+      </c>
+      <c r="F690" s="7" t="n">
+        <v>9878</v>
+      </c>
+      <c r="G690" s="8" t="n">
+        <v>174</v>
+      </c>
+      <c r="H690" s="8" t="n">
+        <v>276</v>
+      </c>
+      <c r="I690" s="8" t="n">
+        <v>503.42</v>
+      </c>
+      <c r="J690" s="8" t="n">
+        <v>20521</v>
+      </c>
+      <c r="K690" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" s="5" t="inlineStr">
+        <is>
+          <t>TBD at Chicago White Sox - ALCS (Game 4, Home Game 2)</t>
+        </is>
+      </c>
+      <c r="B691" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-16T22:00</t>
+        </is>
+      </c>
+      <c r="C691" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-01T03:00</t>
+        </is>
+      </c>
+      <c r="D691" s="6" t="n">
+        <v>379</v>
+      </c>
+      <c r="E691" s="7" t="n">
+        <v>265</v>
+      </c>
+      <c r="F691" s="7" t="n">
+        <v>1230</v>
+      </c>
+      <c r="G691" s="8" t="n">
+        <v>245</v>
+      </c>
+      <c r="H691" s="8" t="n">
+        <v>531</v>
+      </c>
+      <c r="I691" s="8" t="n">
+        <v>903.11</v>
+      </c>
+      <c r="J691" s="8" t="n">
+        <v>13040</v>
+      </c>
+      <c r="K691" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" s="5" t="inlineStr">
+        <is>
+          <t>TBD at Atlanta Braves - NLCS (Home Game 3)</t>
+        </is>
+      </c>
+      <c r="B692" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-17T07:30</t>
+        </is>
+      </c>
+      <c r="C692" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-01T06:00</t>
+        </is>
+      </c>
+      <c r="D692" s="6" t="n">
+        <v>385.5</v>
+      </c>
+      <c r="E692" s="7" t="n">
+        <v>838</v>
+      </c>
+      <c r="F692" s="7" t="n">
+        <v>4757</v>
+      </c>
+      <c r="G692" s="8" t="n">
+        <v>201</v>
+      </c>
+      <c r="H692" s="8" t="n">
+        <v>446</v>
+      </c>
+      <c r="I692" s="8" t="n">
+        <v>802.95</v>
+      </c>
+      <c r="J692" s="8" t="n">
+        <v>17780</v>
+      </c>
+      <c r="K692" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" s="5" t="inlineStr">
+        <is>
+          <t>TBD at New York Yankees - ALCS (Home Game 3)</t>
+        </is>
+      </c>
+      <c r="B693" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-17T07:30</t>
+        </is>
+      </c>
+      <c r="C693" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-01T06:00</t>
+        </is>
+      </c>
+      <c r="D693" s="6" t="n">
+        <v>385.5</v>
+      </c>
+      <c r="E693" s="7" t="n">
+        <v>576</v>
+      </c>
+      <c r="F693" s="7" t="n">
+        <v>2522</v>
+      </c>
+      <c r="G693" s="8" t="n">
+        <v>246</v>
+      </c>
+      <c r="H693" s="8" t="n">
+        <v>623</v>
+      </c>
+      <c r="I693" s="8" t="n">
+        <v>1182.05</v>
+      </c>
+      <c r="J693" s="8" t="n">
+        <v>11988</v>
+      </c>
+      <c r="K693" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" s="5" t="inlineStr">
+        <is>
+          <t>TBD at Chicago White Sox - ALCS (Game 5, Home Game 3)</t>
+        </is>
+      </c>
+      <c r="B694" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-18T00:00</t>
+        </is>
+      </c>
+      <c r="C694" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-01T07:00</t>
+        </is>
+      </c>
+      <c r="D694" s="6" t="n">
+        <v>401</v>
+      </c>
+      <c r="E694" s="7" t="n">
+        <v>175</v>
+      </c>
+      <c r="F694" s="7" t="n">
+        <v>829</v>
+      </c>
+      <c r="G694" s="8" t="n">
+        <v>245</v>
+      </c>
+      <c r="H694" s="8" t="n">
+        <v>530</v>
+      </c>
+      <c r="I694" s="8" t="n">
+        <v>939.5700000000001</v>
+      </c>
+      <c r="J694" s="8" t="n">
+        <v>14225</v>
+      </c>
+      <c r="K694" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" s="5" t="inlineStr">
+        <is>
           <t>TBD at Cleveland Guardians - ALCS (Home Game 3)</t>
         </is>
       </c>
-      <c r="B672" s="5" t="inlineStr">
+      <c r="B695" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-18T00:08</t>
+        </is>
+      </c>
+      <c r="C695" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-01T06:00</t>
+        </is>
+      </c>
+      <c r="D695" s="6" t="n">
+        <v>402.1</v>
+      </c>
+      <c r="E695" s="7" t="n">
+        <v>530</v>
+      </c>
+      <c r="F695" s="7" t="n">
+        <v>2609</v>
+      </c>
+      <c r="G695" s="8" t="n">
+        <v>257</v>
+      </c>
+      <c r="H695" s="8" t="n">
+        <v>506</v>
+      </c>
+      <c r="I695" s="8" t="n">
+        <v>530.84</v>
+      </c>
+      <c r="J695" s="8" t="n">
+        <v>1839</v>
+      </c>
+      <c r="K695" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" s="5" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays at Cleveland Guardians - ALCS (Game 4, Home Game 2) (Formerly Game 5)</t>
+        </is>
+      </c>
+      <c r="B696" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-18T00:08</t>
+        </is>
+      </c>
+      <c r="C696" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-17T12:00</t>
+        </is>
+      </c>
+      <c r="D696" s="6" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="E696" s="7" t="n">
+        <v>734</v>
+      </c>
+      <c r="F696" s="7" t="n">
+        <v>2224</v>
+      </c>
+      <c r="G696" s="8" t="n">
+        <v>121</v>
+      </c>
+      <c r="H696" s="8" t="n">
+        <v>305</v>
+      </c>
+      <c r="I696" s="8" t="n">
+        <v>344.12</v>
+      </c>
+      <c r="J696" s="8" t="n">
+        <v>2388</v>
+      </c>
+      <c r="K696" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="5" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays at Cleveland Guardians - ALCS (Game 4, Home Game 2) (Formerly Game 5)</t>
+        </is>
+      </c>
+      <c r="B697" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-18T00:08</t>
+        </is>
+      </c>
+      <c r="C697" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-17T14:22</t>
+        </is>
+      </c>
+      <c r="D697" s="6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="E697" s="7" t="n">
+        <v>758</v>
+      </c>
+      <c r="F697" s="7" t="n">
+        <v>2206</v>
+      </c>
+      <c r="G697" s="8" t="n">
+        <v>151</v>
+      </c>
+      <c r="H697" s="8" t="n">
+        <v>279.5</v>
+      </c>
+      <c r="I697" s="8" t="n">
+        <v>327.68</v>
+      </c>
+      <c r="J697" s="8" t="n">
+        <v>2388</v>
+      </c>
+      <c r="K697" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" s="5" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays at Cleveland Guardians - ALCS (Game 4, Home Game 2) (Formerly Game 5)</t>
+        </is>
+      </c>
+      <c r="B698" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-18T00:08</t>
+        </is>
+      </c>
+      <c r="C698" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-17T19:00</t>
+        </is>
+      </c>
+      <c r="D698" s="6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="E698" s="7" t="n">
+        <v>610</v>
+      </c>
+      <c r="F698" s="7" t="n">
+        <v>1646</v>
+      </c>
+      <c r="G698" s="8" t="n">
+        <v>141</v>
+      </c>
+      <c r="H698" s="8" t="n">
+        <v>248.5</v>
+      </c>
+      <c r="I698" s="8" t="n">
+        <v>300.05</v>
+      </c>
+      <c r="J698" s="8" t="n">
+        <v>1821</v>
+      </c>
+      <c r="K698" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" s="5" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays at Cleveland Guardians - ALCS (Game 4, Home Game 2) (Formerly Game 5)</t>
+        </is>
+      </c>
+      <c r="B699" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-18T00:08</t>
+        </is>
+      </c>
+      <c r="C699" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-17T22:00</t>
+        </is>
+      </c>
+      <c r="D699" s="6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E699" s="7" t="n">
+        <v>389</v>
+      </c>
+      <c r="F699" s="7" t="n">
+        <v>985</v>
+      </c>
+      <c r="G699" s="8" t="n">
+        <v>128</v>
+      </c>
+      <c r="H699" s="8" t="n">
+        <v>232</v>
+      </c>
+      <c r="I699" s="8" t="n">
+        <v>280.98</v>
+      </c>
+      <c r="J699" s="8" t="n">
+        <v>1991</v>
+      </c>
+      <c r="K699" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" s="5" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays at Cleveland Guardians - ALCS (Game 4, Home Game 2) (Formerly Game 5)</t>
+        </is>
+      </c>
+      <c r="B700" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-18T00:08</t>
+        </is>
+      </c>
+      <c r="C700" s="5" t="inlineStr">
         <is>
           <t>2026-10-18T00:00</t>
         </is>
       </c>
-      <c r="C672" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-01T06:00</t>
-        </is>
-      </c>
-      <c r="D672" s="6" t="n">
-        <v>402</v>
-      </c>
-      <c r="E672" s="7" t="n">
-        <v>530</v>
-      </c>
-      <c r="F672" s="7" t="n">
-        <v>2609</v>
-      </c>
-      <c r="G672" s="8" t="n">
-        <v>257</v>
-      </c>
-      <c r="H672" s="8" t="n">
-        <v>506</v>
-      </c>
-      <c r="I672" s="8" t="n">
-        <v>530.84</v>
-      </c>
-      <c r="J672" s="8" t="n">
-        <v>1839</v>
-      </c>
-      <c r="K672" s="5" t="inlineStr">
+      <c r="D700" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E700" s="7" t="n">
+        <v>162</v>
+      </c>
+      <c r="F700" s="7" t="n">
+        <v>379</v>
+      </c>
+      <c r="G700" s="8" t="n">
+        <v>90</v>
+      </c>
+      <c r="H700" s="8" t="n">
+        <v>202</v>
+      </c>
+      <c r="I700" s="8" t="n">
+        <v>239.11</v>
+      </c>
+      <c r="J700" s="8" t="n">
+        <v>970</v>
+      </c>
+      <c r="K700" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" s="5" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays at Cleveland Guardians - ALCS (Game 5, Home Game 3)</t>
+        </is>
+      </c>
+      <c r="B701" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-18T00:08</t>
+        </is>
+      </c>
+      <c r="C701" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-15T00:00</t>
+        </is>
+      </c>
+      <c r="D701" s="6" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="E701" s="7" t="n">
+        <v>734</v>
+      </c>
+      <c r="F701" s="7" t="n">
+        <v>2906</v>
+      </c>
+      <c r="G701" s="8" t="n">
+        <v>191</v>
+      </c>
+      <c r="H701" s="8" t="n">
+        <v>402.5</v>
+      </c>
+      <c r="I701" s="8" t="n">
+        <v>468.02</v>
+      </c>
+      <c r="J701" s="8" t="n">
+        <v>6063</v>
+      </c>
+      <c r="K701" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" s="5" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays at Cleveland Guardians - ALCS (Game 5, Home Game 3)</t>
+        </is>
+      </c>
+      <c r="B702" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-18T00:08</t>
+        </is>
+      </c>
+      <c r="C702" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-16T00:00</t>
+        </is>
+      </c>
+      <c r="D702" s="6" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="E702" s="7" t="n">
+        <v>780</v>
+      </c>
+      <c r="F702" s="7" t="n">
+        <v>2943</v>
+      </c>
+      <c r="G702" s="8" t="n">
+        <v>104</v>
+      </c>
+      <c r="H702" s="8" t="n">
+        <v>345</v>
+      </c>
+      <c r="I702" s="8" t="n">
+        <v>405.91</v>
+      </c>
+      <c r="J702" s="8" t="n">
+        <v>6063</v>
+      </c>
+      <c r="K702" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" s="5" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays at Cleveland Guardians - ALCS (Game 5, Home Game 3)</t>
+        </is>
+      </c>
+      <c r="B703" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-18T00:08</t>
+        </is>
+      </c>
+      <c r="C703" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-17T00:00</t>
+        </is>
+      </c>
+      <c r="D703" s="6" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="E703" s="7" t="n">
+        <v>673</v>
+      </c>
+      <c r="F703" s="7" t="n">
+        <v>2162</v>
+      </c>
+      <c r="G703" s="8" t="n">
+        <v>175</v>
+      </c>
+      <c r="H703" s="8" t="n">
+        <v>341</v>
+      </c>
+      <c r="I703" s="8" t="n">
+        <v>392.94</v>
+      </c>
+      <c r="J703" s="8" t="n">
+        <v>2388</v>
+      </c>
+      <c r="K703" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" s="5" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers at Los Angeles Dodgers - NLCS (Game 5, Home Game 3)</t>
+        </is>
+      </c>
+      <c r="B704" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-18T10:30</t>
+        </is>
+      </c>
+      <c r="C704" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-14T01:00</t>
+        </is>
+      </c>
+      <c r="D704" s="6" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="E704" s="7" t="n">
+        <v>1879</v>
+      </c>
+      <c r="F704" s="7" t="n">
+        <v>8260</v>
+      </c>
+      <c r="G704" s="8" t="n">
+        <v>96</v>
+      </c>
+      <c r="H704" s="8" t="n">
+        <v>215</v>
+      </c>
+      <c r="I704" s="8" t="n">
+        <v>458.29</v>
+      </c>
+      <c r="J704" s="8" t="n">
+        <v>25693</v>
+      </c>
+      <c r="K704" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" s="5" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers at Los Angeles Dodgers - NLCS (Game 5, Home Game 3)</t>
+        </is>
+      </c>
+      <c r="B705" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-18T10:30</t>
+        </is>
+      </c>
+      <c r="C705" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-15T01:00</t>
+        </is>
+      </c>
+      <c r="D705" s="6" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="E705" s="7" t="n">
+        <v>1802</v>
+      </c>
+      <c r="F705" s="7" t="n">
+        <v>7780</v>
+      </c>
+      <c r="G705" s="8" t="n">
+        <v>112</v>
+      </c>
+      <c r="H705" s="8" t="n">
+        <v>229</v>
+      </c>
+      <c r="I705" s="8" t="n">
+        <v>475.21</v>
+      </c>
+      <c r="J705" s="8" t="n">
+        <v>25693</v>
+      </c>
+      <c r="K705" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" s="5" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers at Los Angeles Dodgers - NLCS (Game 5, Home Game 3)</t>
+        </is>
+      </c>
+      <c r="B706" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-18T10:30</t>
+        </is>
+      </c>
+      <c r="C706" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-16T01:00</t>
+        </is>
+      </c>
+      <c r="D706" s="6" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="E706" s="7" t="n">
+        <v>1747</v>
+      </c>
+      <c r="F706" s="7" t="n">
+        <v>7290</v>
+      </c>
+      <c r="G706" s="8" t="n">
+        <v>91</v>
+      </c>
+      <c r="H706" s="8" t="n">
+        <v>220</v>
+      </c>
+      <c r="I706" s="8" t="n">
+        <v>419.93</v>
+      </c>
+      <c r="J706" s="8" t="n">
+        <v>25693</v>
+      </c>
+      <c r="K706" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" s="5" t="inlineStr">
+        <is>
+          <t>New Orleans Saints at New York Giants</t>
+        </is>
+      </c>
+      <c r="B707" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-18T17:00</t>
+        </is>
+      </c>
+      <c r="C707" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-15T17:00</t>
+        </is>
+      </c>
+      <c r="D707" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="E707" s="7" t="n">
+        <v>605</v>
+      </c>
+      <c r="F707" s="7" t="n">
+        <v>1887</v>
+      </c>
+      <c r="G707" s="8" t="n">
+        <v>111</v>
+      </c>
+      <c r="H707" s="8" t="n">
+        <v>206</v>
+      </c>
+      <c r="I707" s="8" t="n">
+        <v>2040.02</v>
+      </c>
+      <c r="J707" s="8" t="n">
+        <v>254450</v>
+      </c>
+      <c r="K707" s="5" t="inlineStr">
+        <is>
+          <t>nfl_metlife</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" s="5" t="inlineStr">
+        <is>
+          <t>New Orleans Saints at New York Giants</t>
+        </is>
+      </c>
+      <c r="B708" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-18T17:00</t>
+        </is>
+      </c>
+      <c r="C708" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-17T17:00</t>
+        </is>
+      </c>
+      <c r="D708" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="E708" s="7" t="n">
+        <v>456</v>
+      </c>
+      <c r="F708" s="7" t="n">
+        <v>1347</v>
+      </c>
+      <c r="G708" s="8" t="n">
+        <v>115</v>
+      </c>
+      <c r="H708" s="8" t="n">
+        <v>192</v>
+      </c>
+      <c r="I708" s="8" t="n">
+        <v>257.34</v>
+      </c>
+      <c r="J708" s="8" t="n">
+        <v>1991</v>
+      </c>
+      <c r="K708" s="5" t="inlineStr">
+        <is>
+          <t>nfl_metlife</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" s="5" t="inlineStr">
+        <is>
+          <t>New Orleans Saints at New York Giants</t>
+        </is>
+      </c>
+      <c r="B709" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-18T17:00</t>
+        </is>
+      </c>
+      <c r="C709" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-18T14:00</t>
+        </is>
+      </c>
+      <c r="D709" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E709" s="7" t="n">
+        <v>247</v>
+      </c>
+      <c r="F709" s="7" t="n">
+        <v>659</v>
+      </c>
+      <c r="G709" s="8" t="n">
+        <v>104</v>
+      </c>
+      <c r="H709" s="8" t="n">
+        <v>217</v>
+      </c>
+      <c r="I709" s="8" t="n">
+        <v>265.48</v>
+      </c>
+      <c r="J709" s="8" t="n">
+        <v>1465</v>
+      </c>
+      <c r="K709" s="5" t="inlineStr">
+        <is>
+          <t>nfl_metlife</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" s="5" t="inlineStr">
+        <is>
+          <t>TBD at Cleveland Guardians - ALCS (Home Game 2)</t>
+        </is>
+      </c>
+      <c r="B710" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-18T21:08</t>
+        </is>
+      </c>
+      <c r="C710" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-29T14:37</t>
+        </is>
+      </c>
+      <c r="D710" s="6" t="n">
+        <v>462.5</v>
+      </c>
+      <c r="E710" s="7" t="n">
+        <v>534</v>
+      </c>
+      <c r="F710" s="7" t="n">
+        <v>2619</v>
+      </c>
+      <c r="G710" s="8" t="n">
+        <v>241</v>
+      </c>
+      <c r="H710" s="8" t="n">
+        <v>473</v>
+      </c>
+      <c r="I710" s="8" t="n">
+        <v>493.45</v>
+      </c>
+      <c r="J710" s="8" t="n">
+        <v>1657</v>
+      </c>
+      <c r="K710" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" s="5" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays at Cleveland Guardians - ALCS (Game 4, Home Game 2)</t>
+        </is>
+      </c>
+      <c r="B711" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-18T21:08</t>
+        </is>
+      </c>
+      <c r="C711" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-13T22:00</t>
+        </is>
+      </c>
+      <c r="D711" s="6" t="n">
+        <v>119.1</v>
+      </c>
+      <c r="E711" s="7" t="n">
+        <v>1031</v>
+      </c>
+      <c r="F711" s="7" t="n">
+        <v>5450</v>
+      </c>
+      <c r="G711" s="8" t="n">
+        <v>211</v>
+      </c>
+      <c r="H711" s="8" t="n">
+        <v>351</v>
+      </c>
+      <c r="I711" s="8" t="n">
+        <v>382.34</v>
+      </c>
+      <c r="J711" s="8" t="n">
+        <v>2388</v>
+      </c>
+      <c r="K711" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" s="5" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays at Cleveland Guardians - ALCS (Game 4, Home Game 2)</t>
+        </is>
+      </c>
+      <c r="B712" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-18T21:08</t>
+        </is>
+      </c>
+      <c r="C712" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:00</t>
+        </is>
+      </c>
+      <c r="D712" s="6" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="E712" s="7" t="n">
+        <v>819</v>
+      </c>
+      <c r="F712" s="7" t="n">
+        <v>3192</v>
+      </c>
+      <c r="G712" s="8" t="n">
+        <v>175</v>
+      </c>
+      <c r="H712" s="8" t="n">
+        <v>296</v>
+      </c>
+      <c r="I712" s="8" t="n">
+        <v>347.83</v>
+      </c>
+      <c r="J712" s="8" t="n">
+        <v>2388</v>
+      </c>
+      <c r="K712" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" s="5" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays at Cleveland Guardians - ALCS (Game 4, Home Game 2)</t>
+        </is>
+      </c>
+      <c r="B713" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-18T21:08</t>
+        </is>
+      </c>
+      <c r="C713" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-15T22:00</t>
+        </is>
+      </c>
+      <c r="D713" s="6" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="E713" s="7" t="n">
+        <v>803</v>
+      </c>
+      <c r="F713" s="7" t="n">
+        <v>2961</v>
+      </c>
+      <c r="G713" s="8" t="n">
+        <v>117</v>
+      </c>
+      <c r="H713" s="8" t="n">
+        <v>259</v>
+      </c>
+      <c r="I713" s="8" t="n">
+        <v>300.08</v>
+      </c>
+      <c r="J713" s="8" t="n">
+        <v>2388</v>
+      </c>
+      <c r="K713" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" s="5" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays at Cleveland Guardians - ALCS (Game 4, Home Game 2)</t>
+        </is>
+      </c>
+      <c r="B714" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-18T21:08</t>
+        </is>
+      </c>
+      <c r="C714" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-16T10:00</t>
+        </is>
+      </c>
+      <c r="D714" s="6" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="E714" s="7" t="n">
+        <v>790</v>
+      </c>
+      <c r="F714" s="7" t="n">
+        <v>2828</v>
+      </c>
+      <c r="G714" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="H714" s="8" t="n">
+        <v>217</v>
+      </c>
+      <c r="I714" s="8" t="n">
+        <v>253.41</v>
+      </c>
+      <c r="J714" s="8" t="n">
+        <v>2388</v>
+      </c>
+      <c r="K714" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" s="5" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays at Cleveland Guardians - ALCS (Game 4, Home Game 2)</t>
+        </is>
+      </c>
+      <c r="B715" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-18T21:08</t>
+        </is>
+      </c>
+      <c r="C715" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-16T14:00</t>
+        </is>
+      </c>
+      <c r="D715" s="6" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="E715" s="7" t="n">
+        <v>780</v>
+      </c>
+      <c r="F715" s="7" t="n">
+        <v>2772</v>
+      </c>
+      <c r="G715" s="8" t="n">
+        <v>101</v>
+      </c>
+      <c r="H715" s="8" t="n">
+        <v>187</v>
+      </c>
+      <c r="I715" s="8" t="n">
+        <v>235.1</v>
+      </c>
+      <c r="J715" s="8" t="n">
+        <v>2388</v>
+      </c>
+      <c r="K715" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" s="5" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays at Cleveland Guardians - ALCS (Game 4, Home Game 2)</t>
+        </is>
+      </c>
+      <c r="B716" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-18T21:08</t>
+        </is>
+      </c>
+      <c r="C716" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-16T18:00</t>
+        </is>
+      </c>
+      <c r="D716" s="6" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="E716" s="7" t="n">
+        <v>663</v>
+      </c>
+      <c r="F716" s="7" t="n">
+        <v>2153</v>
+      </c>
+      <c r="G716" s="8" t="n">
+        <v>96</v>
+      </c>
+      <c r="H716" s="8" t="n">
+        <v>177</v>
+      </c>
+      <c r="I716" s="8" t="n">
+        <v>221.52</v>
+      </c>
+      <c r="J716" s="8" t="n">
+        <v>2388</v>
+      </c>
+      <c r="K716" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" s="5" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays at Cleveland Guardians - ALCS (Game 4, Home Game 2)</t>
+        </is>
+      </c>
+      <c r="B717" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-18T21:08</t>
+        </is>
+      </c>
+      <c r="C717" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-16T21:00</t>
+        </is>
+      </c>
+      <c r="D717" s="6" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="E717" s="7" t="n">
+        <v>522</v>
+      </c>
+      <c r="F717" s="7" t="n">
+        <v>1666</v>
+      </c>
+      <c r="G717" s="8" t="n">
+        <v>91</v>
+      </c>
+      <c r="H717" s="8" t="n">
+        <v>159</v>
+      </c>
+      <c r="I717" s="8" t="n">
+        <v>208.21</v>
+      </c>
+      <c r="J717" s="8" t="n">
+        <v>2388</v>
+      </c>
+      <c r="K717" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" s="5" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays at Cleveland Guardians - ALCS (Game 4, Home Game 2)</t>
+        </is>
+      </c>
+      <c r="B718" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-18T21:08</t>
+        </is>
+      </c>
+      <c r="C718" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-16T23:00</t>
+        </is>
+      </c>
+      <c r="D718" s="6" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="E718" s="7" t="n">
+        <v>350</v>
+      </c>
+      <c r="F718" s="7" t="n">
+        <v>918</v>
+      </c>
+      <c r="G718" s="8" t="n">
+        <v>62</v>
+      </c>
+      <c r="H718" s="8" t="n">
+        <v>148</v>
+      </c>
+      <c r="I718" s="8" t="n">
+        <v>219.25</v>
+      </c>
+      <c r="J718" s="8" t="n">
+        <v>11684</v>
+      </c>
+      <c r="K718" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" s="5" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays at Cleveland Guardians - ALCS (Game 5, Home Game 3) (Rescheduled Game 4 from 10/16)</t>
+        </is>
+      </c>
+      <c r="B719" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-18T21:08</t>
+        </is>
+      </c>
+      <c r="C719" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-17T22:00</t>
+        </is>
+      </c>
+      <c r="D719" s="6" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="E719" s="7" t="n">
+        <v>480</v>
+      </c>
+      <c r="F719" s="7" t="n">
+        <v>1191</v>
+      </c>
+      <c r="G719" s="8" t="n">
+        <v>187</v>
+      </c>
+      <c r="H719" s="8" t="n">
+        <v>459</v>
+      </c>
+      <c r="I719" s="8" t="n">
+        <v>1141.26</v>
+      </c>
+      <c r="J719" s="8" t="n">
+        <v>117669</v>
+      </c>
+      <c r="K719" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" s="5" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays at Cleveland Guardians - ALCS (Game 5, Home Game 3) (Rescheduled Game 4 from 10/16)</t>
+        </is>
+      </c>
+      <c r="B720" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-18T21:08</t>
+        </is>
+      </c>
+      <c r="C720" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-18T10:00</t>
+        </is>
+      </c>
+      <c r="D720" s="6" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E720" s="7" t="n">
+        <v>583</v>
+      </c>
+      <c r="F720" s="7" t="n">
+        <v>1342</v>
+      </c>
+      <c r="G720" s="8" t="n">
+        <v>147</v>
+      </c>
+      <c r="H720" s="8" t="n">
+        <v>336</v>
+      </c>
+      <c r="I720" s="8" t="n">
+        <v>845.9</v>
+      </c>
+      <c r="J720" s="8" t="n">
+        <v>117669</v>
+      </c>
+      <c r="K720" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" s="5" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays at Cleveland Guardians - ALCS (Game 5, Home Game 3) (Rescheduled Game 4 from 10/16)</t>
+        </is>
+      </c>
+      <c r="B721" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-18T21:08</t>
+        </is>
+      </c>
+      <c r="C721" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-18T16:00</t>
+        </is>
+      </c>
+      <c r="D721" s="6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="E721" s="7" t="n">
+        <v>498</v>
+      </c>
+      <c r="F721" s="7" t="n">
+        <v>1067</v>
+      </c>
+      <c r="G721" s="8" t="n">
+        <v>118</v>
+      </c>
+      <c r="H721" s="8" t="n">
+        <v>260</v>
+      </c>
+      <c r="I721" s="8" t="n">
+        <v>807.25</v>
+      </c>
+      <c r="J721" s="8" t="n">
+        <v>117669</v>
+      </c>
+      <c r="K721" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" s="5" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays at Cleveland Guardians - ALCS (Game 5, Home Game 3) (Rescheduled Game 4 from 10/16)</t>
+        </is>
+      </c>
+      <c r="B722" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-18T21:08</t>
+        </is>
+      </c>
+      <c r="C722" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-18T18:51</t>
+        </is>
+      </c>
+      <c r="D722" s="6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E722" s="7" t="n">
+        <v>249</v>
+      </c>
+      <c r="F722" s="7" t="n">
+        <v>462</v>
+      </c>
+      <c r="G722" s="8" t="n">
+        <v>147</v>
+      </c>
+      <c r="H722" s="8" t="n">
+        <v>282</v>
+      </c>
+      <c r="I722" s="8" t="n">
+        <v>392.61</v>
+      </c>
+      <c r="J722" s="8" t="n">
+        <v>2275</v>
+      </c>
+      <c r="K722" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" s="5" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays at Cleveland Guardians - ALCS (Game 5, Home Game 3) (Rescheduled Game 4 from 10/16)</t>
+        </is>
+      </c>
+      <c r="B723" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-18T21:08</t>
+        </is>
+      </c>
+      <c r="C723" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-18T21:00</t>
+        </is>
+      </c>
+      <c r="D723" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E723" s="7" t="n">
+        <v>33</v>
+      </c>
+      <c r="F723" s="7" t="n">
+        <v>48</v>
+      </c>
+      <c r="G723" s="8" t="n">
+        <v>167</v>
+      </c>
+      <c r="H723" s="8" t="n">
+        <v>374</v>
+      </c>
+      <c r="I723" s="8" t="n">
+        <v>459.27</v>
+      </c>
+      <c r="J723" s="8" t="n">
+        <v>1752</v>
+      </c>
+      <c r="K723" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" s="5" t="inlineStr">
+        <is>
+          <t>Los Angeles Dodgers at Milwaukee Brewers - NLCS (Game 6, Home Game 3)</t>
+        </is>
+      </c>
+      <c r="B724" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-19T00:00</t>
+        </is>
+      </c>
+      <c r="C724" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-16T00:00</t>
+        </is>
+      </c>
+      <c r="D724" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="E724" s="7" t="n">
+        <v>596</v>
+      </c>
+      <c r="F724" s="7" t="n">
+        <v>2562</v>
+      </c>
+      <c r="G724" s="8" t="n">
+        <v>302</v>
+      </c>
+      <c r="H724" s="8" t="n">
+        <v>586</v>
+      </c>
+      <c r="I724" s="8" t="n">
+        <v>695.47</v>
+      </c>
+      <c r="J724" s="8" t="n">
+        <v>4758</v>
+      </c>
+      <c r="K724" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" s="5" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians at Tampa Bay Rays - ALCS (Game 6, Home Game 3)</t>
+        </is>
+      </c>
+      <c r="B725" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-20T00:08</t>
+        </is>
+      </c>
+      <c r="C725" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-17T00:00</t>
+        </is>
+      </c>
+      <c r="D725" s="6" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="E725" s="7" t="n">
+        <v>728</v>
+      </c>
+      <c r="F725" s="7" t="n">
+        <v>3955</v>
+      </c>
+      <c r="G725" s="8" t="n">
+        <v>98</v>
+      </c>
+      <c r="H725" s="8" t="n">
+        <v>244</v>
+      </c>
+      <c r="I725" s="8" t="n">
+        <v>309.21</v>
+      </c>
+      <c r="J725" s="8" t="n">
+        <v>4545</v>
+      </c>
+      <c r="K725" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" s="5" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians at Tampa Bay Rays - ALCS (Game 6, Home Game 3)</t>
+        </is>
+      </c>
+      <c r="B726" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-20T00:08</t>
+        </is>
+      </c>
+      <c r="C726" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-17T14:22</t>
+        </is>
+      </c>
+      <c r="D726" s="6" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="E726" s="7" t="n">
+        <v>741</v>
+      </c>
+      <c r="F726" s="7" t="n">
+        <v>3924</v>
+      </c>
+      <c r="G726" s="8" t="n">
+        <v>90</v>
+      </c>
+      <c r="H726" s="8" t="n">
+        <v>248</v>
+      </c>
+      <c r="I726" s="8" t="n">
+        <v>303.97</v>
+      </c>
+      <c r="J726" s="8" t="n">
+        <v>4545</v>
+      </c>
+      <c r="K726" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" s="5" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians at Tampa Bay Rays - ALCS (Game 6, Home Game 3)</t>
+        </is>
+      </c>
+      <c r="B727" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-20T00:08</t>
+        </is>
+      </c>
+      <c r="C727" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-18T01:00</t>
+        </is>
+      </c>
+      <c r="D727" s="6" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="E727" s="7" t="n">
+        <v>724</v>
+      </c>
+      <c r="F727" s="7" t="n">
+        <v>3751</v>
+      </c>
+      <c r="G727" s="8" t="n">
+        <v>106</v>
+      </c>
+      <c r="H727" s="8" t="n">
+        <v>233</v>
+      </c>
+      <c r="I727" s="8" t="n">
+        <v>291.2</v>
+      </c>
+      <c r="J727" s="8" t="n">
+        <v>4545</v>
+      </c>
+      <c r="K727" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" s="5" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians at Tampa Bay Rays - ALCS (Game 6, Home Game 3)</t>
+        </is>
+      </c>
+      <c r="B728" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-20T00:08</t>
+        </is>
+      </c>
+      <c r="C728" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-19T00:25</t>
+        </is>
+      </c>
+      <c r="D728" s="6" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="E728" s="7" t="n">
+        <v>645</v>
+      </c>
+      <c r="F728" s="7" t="n">
+        <v>3025</v>
+      </c>
+      <c r="G728" s="8" t="n">
+        <v>148</v>
+      </c>
+      <c r="H728" s="8" t="n">
+        <v>276</v>
+      </c>
+      <c r="I728" s="8" t="n">
+        <v>341.43</v>
+      </c>
+      <c r="J728" s="8" t="n">
+        <v>4927</v>
+      </c>
+      <c r="K728" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" s="5" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians at Tampa Bay Rays - ALCS (Game 6, Home Game 3)</t>
+        </is>
+      </c>
+      <c r="B729" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-20T00:08</t>
+        </is>
+      </c>
+      <c r="C729" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-19T13:00</t>
+        </is>
+      </c>
+      <c r="D729" s="6" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E729" s="7" t="n">
+        <v>672</v>
+      </c>
+      <c r="F729" s="7" t="n">
+        <v>2894</v>
+      </c>
+      <c r="G729" s="8" t="n">
+        <v>125</v>
+      </c>
+      <c r="H729" s="8" t="n">
+        <v>270.5</v>
+      </c>
+      <c r="I729" s="8" t="n">
+        <v>338.61</v>
+      </c>
+      <c r="J729" s="8" t="n">
+        <v>4545</v>
+      </c>
+      <c r="K729" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" s="5" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians at Tampa Bay Rays - ALCS (Game 6, Home Game 3)</t>
+        </is>
+      </c>
+      <c r="B730" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-20T00:08</t>
+        </is>
+      </c>
+      <c r="C730" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-19T19:00</t>
+        </is>
+      </c>
+      <c r="D730" s="6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="E730" s="7" t="n">
+        <v>539</v>
+      </c>
+      <c r="F730" s="7" t="n">
+        <v>2256</v>
+      </c>
+      <c r="G730" s="8" t="n">
+        <v>118</v>
+      </c>
+      <c r="H730" s="8" t="n">
+        <v>250</v>
+      </c>
+      <c r="I730" s="8" t="n">
+        <v>312.41</v>
+      </c>
+      <c r="J730" s="8" t="n">
+        <v>4545</v>
+      </c>
+      <c r="K730" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" s="5" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians at Tampa Bay Rays - ALCS (Game 6, Home Game 3)</t>
+        </is>
+      </c>
+      <c r="B731" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-20T00:08</t>
+        </is>
+      </c>
+      <c r="C731" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-19T22:00</t>
+        </is>
+      </c>
+      <c r="D731" s="6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E731" s="7" t="n">
+        <v>371</v>
+      </c>
+      <c r="F731" s="7" t="n">
+        <v>1456</v>
+      </c>
+      <c r="G731" s="8" t="n">
+        <v>101</v>
+      </c>
+      <c r="H731" s="8" t="n">
+        <v>190</v>
+      </c>
+      <c r="I731" s="8" t="n">
+        <v>264.65</v>
+      </c>
+      <c r="J731" s="8" t="n">
+        <v>5112</v>
+      </c>
+      <c r="K731" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" s="5" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians at Tampa Bay Rays - ALCS (Game 6, Home Game 3)</t>
+        </is>
+      </c>
+      <c r="B732" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-20T00:08</t>
+        </is>
+      </c>
+      <c r="C732" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-20T00:00</t>
+        </is>
+      </c>
+      <c r="D732" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E732" s="7" t="n">
+        <v>134</v>
+      </c>
+      <c r="F732" s="7" t="n">
+        <v>399</v>
+      </c>
+      <c r="G732" s="8" t="n">
+        <v>91</v>
+      </c>
+      <c r="H732" s="8" t="n">
+        <v>175</v>
+      </c>
+      <c r="I732" s="8" t="n">
+        <v>207.63</v>
+      </c>
+      <c r="J732" s="8" t="n">
+        <v>856</v>
+      </c>
+      <c r="K732" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" s="5" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians at Tampa Bay Rays - ALCS (Game 7, Home Game 4)</t>
+        </is>
+      </c>
+      <c r="B733" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-21T00:08</t>
+        </is>
+      </c>
+      <c r="C733" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-18T01:00</t>
+        </is>
+      </c>
+      <c r="D733" s="6" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="E733" s="7" t="n">
+        <v>736</v>
+      </c>
+      <c r="F733" s="7" t="n">
+        <v>4374</v>
+      </c>
+      <c r="G733" s="8" t="n">
+        <v>111</v>
+      </c>
+      <c r="H733" s="8" t="n">
+        <v>260</v>
+      </c>
+      <c r="I733" s="8" t="n">
+        <v>362.7</v>
+      </c>
+      <c r="J733" s="8" t="n">
+        <v>8754</v>
+      </c>
+      <c r="K733" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" s="5" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians at Tampa Bay Rays - ALCS (Game 7, Home Game 4)</t>
+        </is>
+      </c>
+      <c r="B734" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-21T00:08</t>
+        </is>
+      </c>
+      <c r="C734" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-19T00:25</t>
+        </is>
+      </c>
+      <c r="D734" s="6" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="E734" s="7" t="n">
+        <v>735</v>
+      </c>
+      <c r="F734" s="7" t="n">
+        <v>4056</v>
+      </c>
+      <c r="G734" s="8" t="n">
+        <v>118</v>
+      </c>
+      <c r="H734" s="8" t="n">
+        <v>296</v>
+      </c>
+      <c r="I734" s="8" t="n">
+        <v>409.82</v>
+      </c>
+      <c r="J734" s="8" t="n">
+        <v>11537</v>
+      </c>
+      <c r="K734" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" s="5" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians at Tampa Bay Rays - ALCS (Game 7, Home Game 4)</t>
+        </is>
+      </c>
+      <c r="B735" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-21T00:08</t>
+        </is>
+      </c>
+      <c r="C735" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-20T01:00</t>
+        </is>
+      </c>
+      <c r="D735" s="6" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="E735" s="7" t="n">
+        <v>932</v>
+      </c>
+      <c r="F735" s="7" t="n">
+        <v>5428</v>
+      </c>
+      <c r="G735" s="8" t="n">
+        <v>111</v>
+      </c>
+      <c r="H735" s="8" t="n">
+        <v>269.5</v>
+      </c>
+      <c r="I735" s="8" t="n">
+        <v>355.26</v>
+      </c>
+      <c r="J735" s="8" t="n">
+        <v>6567</v>
+      </c>
+      <c r="K735" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" s="5" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays at Milwaukee Brewers - World Series (Game 1, Home Game 1)</t>
+        </is>
+      </c>
+      <c r="B736" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:00</t>
+        </is>
+      </c>
+      <c r="C736" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-21T00:00</t>
+        </is>
+      </c>
+      <c r="D736" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="E736" s="7" t="n">
+        <v>248</v>
+      </c>
+      <c r="F736" s="7" t="n">
+        <v>590</v>
+      </c>
+      <c r="G736" s="8" t="n">
+        <v>2836</v>
+      </c>
+      <c r="H736" s="8" t="n">
+        <v>4545</v>
+      </c>
+      <c r="I736" s="8" t="n">
+        <v>4967.88</v>
+      </c>
+      <c r="J736" s="8" t="n">
+        <v>17655</v>
+      </c>
+      <c r="K736" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" s="5" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays at Milwaukee Brewers - World Series (Game 1, Home Game 1)</t>
+        </is>
+      </c>
+      <c r="B737" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:00</t>
+        </is>
+      </c>
+      <c r="C737" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22T00:00</t>
+        </is>
+      </c>
+      <c r="D737" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="E737" s="7" t="n">
+        <v>274</v>
+      </c>
+      <c r="F737" s="7" t="n">
+        <v>767</v>
+      </c>
+      <c r="G737" s="8" t="n">
+        <v>2331</v>
+      </c>
+      <c r="H737" s="8" t="n">
+        <v>3977</v>
+      </c>
+      <c r="I737" s="8" t="n">
+        <v>4544.93</v>
+      </c>
+      <c r="J737" s="8" t="n">
+        <v>17655</v>
+      </c>
+      <c r="K737" s="5" t="inlineStr">
+        <is>
+          <t>mlb_postseason</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" s="5" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays at Milwaukee Brewers - World Series (Game 2, Home Game 2)</t>
+        </is>
+      </c>
+      <c r="B738" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-25T00:00</t>
+        </is>
+      </c>
+      <c r="C738" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22T00:00</t>
+        </is>
+      </c>
+      <c r="D738" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="E738" s="7" t="n">
+        <v>416</v>
+      </c>
+      <c r="F738" s="7" t="n">
+        <v>1149</v>
+      </c>
+      <c r="G738" s="8" t="n">
+        <v>2105</v>
+      </c>
+      <c r="H738" s="8" t="n">
+        <v>3943.5</v>
+      </c>
+      <c r="I738" s="8" t="n">
+        <v>4279.16</v>
+      </c>
+      <c r="J738" s="8" t="n">
+        <v>19420</v>
+      </c>
+      <c r="K738" s="5" t="inlineStr">
         <is>
           <t>mlb_postseason</t>
         </is>
@@ -33813,7 +37448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -33877,109 +37512,109 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Cleveland Guardians at Tampa Bay Rays - ALCS (Game 1, Home Game 1)</t>
+          <t>Tampa Bay Rays at Milwaukee Brewers - World Series (Game 1, Home Game 1)</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13T00:00</t>
+          <t>2026-10-24T00:00</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>2026-10-12T20:00</t>
+          <t>2026-10-23T19:00</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr"/>
       <c r="E2" s="5" t="inlineStr">
         <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
           <t>Tampa Bay Rays</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>Cleveland Guardians</t>
-        </is>
-      </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>Saint Petersburg</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13T01:00</t>
+          <t>2026-10-24T01:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Cleveland Guardians at Tampa Bay Rays - ALCS (Game 2, Home Game 2)</t>
+          <t>Tampa Bay Rays at Milwaukee Brewers - World Series (Game 2, Home Game 2)</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>2026-10-14T00:00</t>
+          <t>2026-10-25T00:00</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13T20:00</t>
+          <t>2026-10-24T19:00</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr"/>
       <c r="E3" s="5" t="inlineStr">
         <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
           <t>Tampa Bay Rays</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>Cleveland Guardians</t>
-        </is>
-      </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>Saint Petersburg</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>2026-10-14T01:00</t>
+          <t>2026-10-25T01:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers at Los Angeles Dodgers - NLCS (Game 3, Home Game 1)</t>
+          <t>Milwaukee Brewers at Tampa Bay Rays - World Series (Game 3, Home Game 1)</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>2026-10-15T00:00</t>
+          <t>2026-10-27T00:00</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>2026-10-14T17:00</t>
+          <t>2026-10-26T20:00</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr"/>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>Tampa Bay Rays</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
@@ -33989,83 +37624,83 @@
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Saint Petersburg</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>2026-10-15T01:30</t>
+          <t>2026-10-27T01:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays at Cleveland Guardians - ALCS (Game 3, Home Game 1)</t>
+          <t>Milwaukee Brewers at Tampa Bay Rays - World Series (Game 4, Home Game 2)</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2026-10-15T22:00</t>
+          <t>2026-10-28T00:00</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>2026-10-15T18:00</t>
+          <t>2026-10-27T20:00</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr"/>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Cleveland Guardians</t>
+          <t>Tampa Bay Rays</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Saint Petersburg</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>2026-10-15T22:00</t>
+          <t>2026-10-28T01:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers at Los Angeles Dodgers - NLCS (Game 4, Home Game 2)</t>
+          <t>Milwaukee Brewers at Tampa Bay Rays - World Series (Game 5, Home Game 3)</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>2026-10-16T01:00</t>
+          <t>2026-10-29T00:00</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>2026-10-15T18:00</t>
+          <t>2026-10-28T20:00</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr"/>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>Tampa Bay Rays</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -34075,40 +37710,40 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Saint Petersburg</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>2026-10-16T02:30</t>
+          <t>2026-10-29T01:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays at Cleveland Guardians - ALCS (Game 4, Home Game 2)</t>
+          <t>Tampa Bay Rays at Milwaukee Brewers - World Series (Game 6, Home Game 3)</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>2026-10-16T22:00</t>
+          <t>2026-10-31T00:00</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>2026-10-16T18:00</t>
+          <t>2026-10-30T19:00</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr"/>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Cleveland Guardians</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -34118,877 +37753,60 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>2026-10-16T22:00</t>
+          <t>2026-10-31T01:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers at Los Angeles Dodgers - NLCS (Game 5, Home Game 3)</t>
+          <t>Tampa Bay Rays at Milwaukee Brewers - World Series (Game 7, Home Game 4)</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>2026-10-17T01:00</t>
+          <t>2026-11-01T00:00</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>2026-10-16T18:00</t>
+          <t>2026-10-31T19:00</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr"/>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Tampa Bay Rays</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>2026-10-17T02:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Tampa Bay Rays at Cleveland Guardians - ALCS (Game 5, Home Game 3)</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-18T00:00</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-17T20:00</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr"/>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Cleveland Guardians</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>Tampa Bay Rays</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>Progressive Field</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>Cleveland</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-18T00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Los Angeles Dodgers at Milwaukee Brewers - NLCS (Game 6, Home Game 3)</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-19T00:00</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-18T19:00</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>Milwaukee Brewers</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>Los Angeles Dodgers</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>American Family Field</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>Milwaukee</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-19T01:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Cleveland Guardians at Tampa Bay Rays - ALCS (Game 6, Home Game 3)</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-19T21:00</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-19T17:00</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>Tampa Bay Rays</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>Cleveland Guardians</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>Tropicana Field</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>Saint Petersburg</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-19T22:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Los Angeles Dodgers at Milwaukee Brewers - NLCS (Game 7, Home Game 4)</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-20T00:00</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-19T19:00</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>Milwaukee Brewers</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>Los Angeles Dodgers</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>American Family Field</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>Milwaukee</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Cleveland Guardians at Tampa Bay Rays - ALCS (Game 7, Home Game 4)</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-21T00:00</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-20T20:00</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr"/>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>Tampa Bay Rays</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>Cleveland Guardians</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>Tropicana Field</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>Saint Petersburg</t>
-        </is>
-      </c>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-21T01:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>TBD at Milwaukee Brewers - World Series (Game 1, Home Game 1)</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-23T08:30</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-23T03:30</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>Milwaukee Brewers</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>American Family Field</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>Milwaukee</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-23T09:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>TBD at Los Angeles Dodgers - World Series (Game 1, Home Game 1)</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-23T10:30</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-23T03:30</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>Los Angeles Dodgers</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>Los Angeles</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-23T12:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>TBD at Milwaukee Brewers - World Series (Game 2, Home Game 2)</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-24T08:30</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-24T03:30</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>Milwaukee Brewers</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>American Family Field</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>Milwaukee</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-24T09:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>TBD at Los Angeles Dodgers - World Series (Game 2, Home Game 2)</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-24T10:30</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-24T03:30</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>Los Angeles Dodgers</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>Los Angeles</t>
-        </is>
-      </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-24T12:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>TBD at Tampa Bay Rays - World Series (Game 3, Home Game 1)</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-26T07:30</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-26T03:30</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>Tampa Bay Rays</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>Tropicana Field</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>Saint Petersburg</t>
-        </is>
-      </c>
-      <c r="I18" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-26T08:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>TBD at Cleveland Guardians - World Series (Game 3, Home Game 1)</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-26T07:30</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-26T03:30</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>Cleveland Guardians</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>Progressive Field</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>Cleveland</t>
-        </is>
-      </c>
-      <c r="I19" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-26T07:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>TBD at Cleveland Guardians - World Series (Game 4, Home Game 2)</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-27T07:30</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-27T03:30</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>Cleveland Guardians</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>Progressive Field</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>Cleveland</t>
-        </is>
-      </c>
-      <c r="I20" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-27T07:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>TBD at Tampa Bay Rays - World Series (Game 4, Home Game 2)</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-27T07:30</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-27T03:30</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>Tampa Bay Rays</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>Tropicana Field</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>Saint Petersburg</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-27T08:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>TBD at Cleveland Guardians - World Series (Game 5, Home Game 3)</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-28T07:30</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-28T03:30</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>Cleveland Guardians</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>Progressive Field</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>Cleveland</t>
-        </is>
-      </c>
-      <c r="I22" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-28T07:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>TBD at Tampa Bay Rays - World Series (Game 5, Home Game 3)</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-28T07:30</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-28T03:30</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>Tampa Bay Rays</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>Tropicana Field</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>Saint Petersburg</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-28T08:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>TBD at Milwaukee Brewers - World Series (Game 6, Home Game 3)</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-30T08:30</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-30T03:30</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>Milwaukee Brewers</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="n"/>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>American Family Field</t>
-        </is>
-      </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>Milwaukee</t>
-        </is>
-      </c>
-      <c r="I24" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-30T09:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>TBD at Los Angeles Dodgers - World Series (Game 6, Home Game 3)</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-30T10:30</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-30T03:30</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>Los Angeles Dodgers</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="n"/>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>Los Angeles</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-30T12:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>TBD at Milwaukee Brewers - World Series (Game 7, Home Game 4)</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-31T08:30</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-31T03:30</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>Milwaukee Brewers</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="n"/>
-      <c r="G26" s="5" t="inlineStr">
-        <is>
-          <t>American Family Field</t>
-        </is>
-      </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>Milwaukee</t>
-        </is>
-      </c>
-      <c r="I26" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-31T09:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>TBD at Los Angeles Dodgers - World Series (Game 7, Home Game 4)</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-31T10:30</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-31T03:30</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>Los Angeles Dodgers</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="n"/>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>Los Angeles</t>
-        </is>
-      </c>
-      <c r="I27" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-31T12:00</t>
+          <t>2026-11-01T01:00</t>
         </is>
       </c>
     </row>
@@ -35006,7 +37824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -35064,17 +37882,17 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Cleveland Guardians at Tampa Bay Rays: ALCS (Home Game 1)</t>
+          <t>Tampa Bay Rays at Milwaukee Brewers: World Series (Home Game 1)</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
@@ -35084,12 +37902,12 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>Saint Petersburg</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
@@ -35099,24 +37917,24 @@
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13T01:30</t>
+          <t>2026-10-24T01:30</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers at Milwaukee Brewers: NLCS (Home Game 2)</t>
+          <t>Tampa Bay Rays at Milwaukee Brewers: World Series (Home Game 2)</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -35141,19 +37959,19 @@
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>2026-10-12T22:30</t>
+          <t>2026-10-25T01:30</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Cleveland Guardians at Tampa Bay Rays: ALCS (Home Game 2)</t>
+          <t>Milwaukee Brewers at Tampa Bay Rays: World Series (Home Game 1)</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -35183,100 +38001,108 @@
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>2026-10-14T01:30</t>
+          <t>2026-10-27T01:30</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Atlanta Braves NLCS Home Game 1</t>
+          <t>Milwaukee Brewers at Tampa Bay Rays: World Series (Home Game 2)</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n"/>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>onsale</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Saint Petersburg</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>2026-09-17T17:00</t>
+          <t>1900-01-01T18:00</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>2026-10-14T05:00</t>
+          <t>2026-10-28T01:30</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Atlanta Braves NLCS Home Game 1 * Premium Seating *</t>
+          <t>Milwaukee Brewers at Tampa Bay Rays: World Series (Home Game 3, If Necessary)</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="n"/>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>onsale</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Saint Petersburg</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>2026-09-17T17:00</t>
+          <t>1900-01-01T18:00</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>2026-10-14T05:00</t>
+          <t>2026-10-29T01:30</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers at Los Angeles Dodgers: NLCS (Home Game 1)</t>
+          <t>Tampa Bay Rays at Milwaukee Brewers: World Series (Home Game 3, If Necessary)</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -35286,12 +38112,12 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -35301,765 +38127,49 @@
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>2026-10-15T02:00</t>
+          <t>2026-10-31T01:30</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>ALCS Home Game 1</t>
+          <t>Tampa Bay Rays at Milwaukee Brewers: World Series (Home Game 4, If Necessary)</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="n"/>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>onsale</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>2026-09-18T19:00</t>
+          <t>1900-01-01T18:00</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>2026-10-16T02:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Atlanta Braves NLCS Home Game 2</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Truist Park</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>Atlanta</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-17T17:00</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-15T05:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Atlanta Braves NLCS Home Game 2 * Premium Seating *</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>Truist Park</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>Atlanta</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-17T17:00</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-15T05:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Milwaukee Brewers at Los Angeles Dodgers: NLCS (Home Game 2)</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>18:00:00</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>onsale</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>Los Angeles</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>1900-01-01T18:00</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-16T03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Tampa Bay Rays at Cleveland Guardians: ALCS (Home Game 1)</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>18:00:00</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>onsale</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>Progressive Field</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>Cleveland</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>1900-01-01T18:00</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-15T22:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>ALCS Home Game 2</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>Rate Field</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>Chicago</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-18T19:00</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-17T02:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>Atlanta Braves NLCS Home Game 3</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>Truist Park</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>Atlanta</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-17T17:00</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-16T05:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Atlanta Braves NLCS Home Game 3 * Premium Seating *</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>Truist Park</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>Atlanta</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-17T17:00</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-16T05:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>Milwaukee Brewers at Los Angeles Dodgers: NLCS (Home Game 3, If Necessary)</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>18:00:00</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>onsale</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>Los Angeles</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>1900-01-01T18:00</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-17T03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>NLCS Home Game 3</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>Chase Field</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-25T16:00</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-17T05:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>Tampa Bay Rays at Cleveland Guardians: ALCS (Home Game 2)</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>18:00:00</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>onsale</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>Progressive Field</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>Cleveland</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>1900-01-01T18:00</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-16T22:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>ALCS HOME GM3 (If Necessary)</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>Rate Field</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>Chicago</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-18T19:00</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-18T02:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>Tampa Bay Rays at Cleveland Guardians: ALCS (Home Game 3, If Necessary)</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>20:00:00</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>onsale</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>Progressive Field</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>Cleveland</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>1900-01-01T18:00</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-18T00:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>Los Angeles Dodgers at Milwaukee Brewers: NLCS (Home Game 3, If Necessary)</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>19:00:00</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>onsale</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>American Family Field</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>Milwaukee</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>1900-01-01T18:00</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-19T01:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>Atlanta Braves NLCS Home Game 4</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>Truist Park</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>Atlanta</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-17T17:00</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-19T05:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>Atlanta Braves NLCS Home Game 4 * Premium Seating *</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="n"/>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>Truist Park</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>Atlanta</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-17T17:00</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-19T05:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>Cleveland Guardians at Tampa Bay Rays: ALCS (Home Game 3, If Necessary)</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>17:00:00</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>onsale</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>Tropicana Field</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>Saint Petersburg</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>1900-01-01T18:00</t>
-        </is>
-      </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-19T22:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>Los Angeles Dodgers at Milwaukee Brewers: NLCS (Home Game 4, If Necessary)</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>19:00:00</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>onsale</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>American Family Field</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>Milwaukee</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>1900-01-01T18:00</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>Cleveland Guardians at Tampa Bay Rays: ALCS (Home Game 4, If Necessary)</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>20:00:00</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>onsale</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>Tropicana Field</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>Saint Petersburg</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr">
-        <is>
-          <t>1900-01-01T18:00</t>
-        </is>
-      </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-21T01:30</t>
+          <t>2026-11-01T01:30</t>
         </is>
       </c>
     </row>
